--- a/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
@@ -12,21 +12,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부품 검토자료" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="reply_containment_scope">'대책서'!$B$21</definedName>
-    <definedName name="reply_containment">'대책서'!$B$22</definedName>
-    <definedName name="reply_root_cause_label">'대책서'!$B$25</definedName>
-    <definedName name="reply_root_cause">'대책서'!$B$26</definedName>
-    <definedName name="reply_escape_cause">'대책서'!$B$28</definedName>
-    <definedName name="reply_prevention">'대책서'!$B$31</definedName>
-    <definedName name="reply_verify_period">'검증'!$B$5</definedName>
-    <definedName name="reply_verify_recipe">'검증'!$D$5</definedName>
-    <definedName name="reply_verify_inspected">'검증'!$E$5</definedName>
-    <definedName name="reply_verify_defective">'검증'!$F$5</definedName>
-    <definedName name="reply_verify_status">'검증'!$H$5</definedName>
-    <definedName name="reply_verify_note">'검증'!$B$6</definedName>
-    <definedName name="reply_closed_at">'검증'!$F$8</definedName>
-    <definedName name="reply_closure_note">'검증'!$B$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$L$42</definedName>
+    <definedName name="reply_containment_scope">'대책서'!$C$18</definedName>
+    <definedName name="reply_containment">'대책서'!$C$19</definedName>
+    <definedName name="reply_root_cause_label">'대책서'!$C$20</definedName>
+    <definedName name="reply_root_cause">'대책서'!$C$21</definedName>
+    <definedName name="reply_escape_cause">'대책서'!$C$22</definedName>
+    <definedName name="reply_prevention">'대책서'!$C$23</definedName>
+    <definedName name="reply_verify_period">'대책서'!$C$25</definedName>
+    <definedName name="reply_verify_recipe">'대책서'!$E$25</definedName>
+    <definedName name="reply_verify_inspected">'대책서'!$G$25</definedName>
+    <definedName name="reply_verify_defective">'대책서'!$I$25</definedName>
+    <definedName name="reply_verify_status">'대책서'!$K$25</definedName>
+    <definedName name="reply_verify_note">'대책서'!$C$27</definedName>
+    <definedName name="reply_closed_at">'대책서'!$E$28</definedName>
+    <definedName name="reply_closure_note">'대책서'!$C$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$L$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'불량 근거'!$A$1:$E$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'부품 검토자료'!$A$1:$F$21</definedName>
   </definedNames>
@@ -40,7 +40,7 @@
     <numFmt numFmtId="164" formatCode="0.0&quot;배&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -230,6 +230,11 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="00263445"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -273,8 +278,80 @@
       <color rgb="0080601B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00243D5B"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00243D5B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00243D5B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00262626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00262626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="0069727D"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="0069727D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00516276"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="0069727D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00243D5B"/>
+      <sz val="17"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00243D5B"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -346,8 +423,13 @@
         <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F3F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -487,11 +569,199 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC3CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC3CC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC3CC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC3CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -653,9 +923,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="27" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="27" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -689,31 +962,31 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -723,24 +996,201 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="45" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="7" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="7" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
@@ -771,6 +1221,39 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFF4D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00216348"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00EEF5F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C2A2A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F9EEEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="0080601B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF9EB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -853,14 +1336,98 @@
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="C16" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>부품 식별자: {{part_id}}</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>제조사 P/N·정격·공급사 (이전 v2)
+{{datasheet_match}} · {{selected_mpn}}
+정격 {{selected_spec}} · 공급사 {{selected_supplier}}
+자세한 비교는 「부품 검토자료」 참조.</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>시스템은 배정 대기만 초기 기입합니다. 실제 주관 담당자는 관리자가 작성합니다.</t>
+      </text>
+    </comment>
+    <comment ref="J7" authorId="0" shapeId="0">
+      <text>
+        <t>시스템은 담당자 입력만 초기 기입합니다. 실제 협조 부서는 관리자가 작성합니다.</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>문서 상태와 회신 기한은 시스템이 ISSUED / 담당자 입력으로 초기화하며 이후 관리자가 갱신합니다. Job 상태 또는 DB의 메일 전송 상태와 별개입니다.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>시스템 자동 기입. 발행 검사 시각까지 동일 Job의 검사 완료 Unit 수 × 해당 부품 슬롯 수입니다. requested_quantity(목표 PASS 수량)가 아닙니다.</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>시스템 자동 기입. 동일 Job·부품·불량 유형의 production.unit_defects 기록 수입니다. 불량 Unit 수와 다를 수 있습니다.</t>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0" shapeId="0">
+      <text>
+        <t>자동 계산. 관리자가 아래 검증 검사 수량·불량 수량을 입력하면 PPM을 계산합니다. 검사 시스템에서 재집계해 자동 채우는 값은 아닙니다.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>시스템 자동 기입. 동일 Job 시작(없으면 요청) 시각부터 대상 검사 시각까지 누적 집계합니다. 기간 일수: {{window_days}}. 이동 7일 집계가 아닙니다.</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>발행 시점 전체 슬롯 분포: {{hotspot}}
+전체 분포는 불량 근거 시트에 자동 기입됩니다.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
       <text>
         <t>② 발생 원인의 핵심을 한 줄로 요약합니다.</t>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0">
+    <comment ref="F26" authorId="0" shapeId="0">
       <text>
-        <t>④의 상세 대책을 한두 문장으로 요약합니다. 상세 내용 변경 시 함께 갱신하세요.</t>
+        <t>자동 계산. 검증 불량 수량 ÷ 검증 검사 수량. 검증 수량은 부품 검사 건수 기준입니다.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>기존 생성기가 불량 기록별 Unit ID·검사 시각을 줄바꿈 목록으로 기입합니다. 슬롯 토큰은 중복 제거된 목록이며 개별 기록의 슬롯 열과 일대일 대응하지 않습니다. 운영 적용 전 목록 출력 경계의 정비가 필요합니다.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>현재 생성기는 후보별 행을 늘리지 않고 각 열에 줄바꿈 목록을 기입합니다. 후보 수가 늘거나 항목별 줄바꿈이 달라지면 행 단위 비교가 어려우므로 운영 적용 전 행 확장 검토가 필요합니다.</t>
       </text>
     </comment>
   </commentList>
@@ -1214,933 +1781,746 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
+    <tabColor rgb="00243D5B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7.3" customWidth="1" min="1" max="1"/>
-    <col width="7.3" customWidth="1" min="2" max="2"/>
-    <col width="7.3" customWidth="1" min="3" max="3"/>
-    <col width="7.3" customWidth="1" min="4" max="4"/>
-    <col width="7.3" customWidth="1" min="5" max="5"/>
-    <col width="7.3" customWidth="1" min="6" max="6"/>
-    <col width="7.3" customWidth="1" min="7" max="7"/>
-    <col width="7.3" customWidth="1" min="8" max="8"/>
-    <col width="7.3" customWidth="1" min="9" max="9"/>
-    <col width="7.3" customWidth="1" min="10" max="10"/>
-    <col width="7.3" customWidth="1" min="11" max="11"/>
-    <col width="7.3" customWidth="1" min="12" max="12"/>
+    <col width="6.4" customWidth="1" min="1" max="1"/>
+    <col width="6.4" customWidth="1" min="2" max="2"/>
+    <col width="6.4" customWidth="1" min="3" max="3"/>
+    <col width="6.4" customWidth="1" min="4" max="4"/>
+    <col width="6.4" customWidth="1" min="5" max="5"/>
+    <col width="6.4" customWidth="1" min="6" max="6"/>
+    <col width="6.4" customWidth="1" min="7" max="7"/>
+    <col width="6.4" customWidth="1" min="8" max="8"/>
+    <col width="6.4" customWidth="1" min="9" max="9"/>
+    <col width="6.4" customWidth="1" min="10" max="10"/>
+    <col width="6.4" customWidth="1" min="11" max="11"/>
+    <col width="6.4" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="44" t="inlineStr">
-        <is>
-          <t>불량 대책서</t>
-        </is>
-      </c>
-      <c r="J1" s="45" t="inlineStr">
-        <is>
-          <t>v2  /  검토용</t>
-        </is>
-      </c>
-      <c r="K1" s="46" t="n"/>
-      <c r="L1" s="46" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="47" t="inlineStr">
-        <is>
-          <t>01  현황 · 초동 조치     /     02  원인 · 대책 · 검증 · 종결</t>
-        </is>
-      </c>
-      <c r="J2" s="48" t="inlineStr">
-        <is>
-          <t>{{part_id}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="91" t="inlineStr">
+        <is>
+          <t>불 량 대 책 서</t>
+        </is>
+      </c>
+      <c r="G1" s="122" t="inlineStr">
+        <is>
+          <t>작성</t>
+        </is>
+      </c>
+      <c r="H1" s="123" t="n"/>
+      <c r="I1" s="122" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="J1" s="123" t="n"/>
+      <c r="K1" s="122" t="inlineStr">
+        <is>
+          <t>승인</t>
+        </is>
+      </c>
+      <c r="L1" s="123" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="G2" s="124" t="n"/>
+      <c r="H2" s="125" t="n"/>
+      <c r="I2" s="124" t="n"/>
+      <c r="J2" s="125" t="n"/>
+      <c r="K2" s="124" t="n"/>
+      <c r="L2" s="125" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="G3" s="126" t="n"/>
+      <c r="H3" s="127" t="n"/>
+      <c r="I3" s="126" t="n"/>
+      <c r="J3" s="127" t="n"/>
+      <c r="K3" s="126" t="n"/>
+      <c r="L3" s="127" t="n"/>
+    </row>
+    <row r="4" ht="12" customHeight="1">
+      <c r="A4" s="128" t="inlineStr">
+        <is>
+          <t>시스템 자동 기입 · 발행 시점 고정  |  담당·기한·문서 상태는 관리자 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="122" t="inlineStr">
         <is>
           <t>문서번호</t>
         </is>
       </c>
-      <c r="B3" s="46" t="n"/>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="B5" s="123" t="n"/>
+      <c r="C5" s="129" t="inlineStr">
         <is>
           <t>{{alert_code}}</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
+      <c r="D5" s="130" t="n"/>
+      <c r="E5" s="130" t="n"/>
+      <c r="F5" s="130" t="n"/>
+      <c r="G5" s="123" t="n"/>
+      <c r="H5" s="122" t="inlineStr">
         <is>
           <t>발행일시</t>
         </is>
       </c>
-      <c r="I3" s="46" t="n"/>
-      <c r="J3" s="51" t="inlineStr">
+      <c r="I5" s="123" t="n"/>
+      <c r="J5" s="131" t="inlineStr">
         <is>
           <t>{{issued_at}}</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="K5" s="130" t="n"/>
+      <c r="L5" s="123" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="122" t="inlineStr">
         <is>
           <t>대상 부품</t>
         </is>
       </c>
-      <c r="B4" s="46" t="n"/>
-      <c r="C4" s="50" t="inlineStr">
+      <c r="B6" s="123" t="n"/>
+      <c r="C6" s="129" t="inlineStr">
         <is>
           <t>{{part_id}} · {{part_name}} ({{category_label}})</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="D6" s="130" t="n"/>
+      <c r="E6" s="130" t="n"/>
+      <c r="F6" s="130" t="n"/>
+      <c r="G6" s="123" t="n"/>
+      <c r="H6" s="122" t="inlineStr">
         <is>
           <t>불량 유형</t>
         </is>
       </c>
-      <c r="I4" s="46" t="n"/>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="I6" s="123" t="n"/>
+      <c r="J6" s="131" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="K6" s="130" t="n"/>
+      <c r="L6" s="123" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="122" t="inlineStr">
         <is>
           <t>주관 담당</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n"/>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="B7" s="123" t="n"/>
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>{{assignee}}</t>
         </is>
       </c>
-      <c r="H5" s="49" t="inlineStr">
+      <c r="D7" s="133" t="n"/>
+      <c r="E7" s="133" t="n"/>
+      <c r="F7" s="133" t="n"/>
+      <c r="G7" s="134" t="n"/>
+      <c r="H7" s="122" t="inlineStr">
         <is>
           <t>협조 부서</t>
         </is>
       </c>
-      <c r="I5" s="46" t="n"/>
-      <c r="J5" s="51" t="inlineStr">
+      <c r="I7" s="123" t="n"/>
+      <c r="J7" s="135" t="inlineStr">
         <is>
           <t>{{support_teams}}</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="K7" s="133" t="n"/>
+      <c r="L7" s="134" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="122" t="inlineStr">
         <is>
           <t>발행 대상</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="50" t="inlineStr">
-        <is>
-          <t>Job {{job_id}} · Unit {{target_unit_id}} · {{target_slot_code}}</t>
-        </is>
-      </c>
-      <c r="H6" s="49" t="inlineStr">
+      <c r="B8" s="123" t="n"/>
+      <c r="C8" s="136" t="inlineStr">
+        <is>
+          <t>Job {{job_id}}
+Unit {{target_unit_id}} · {{target_slot_code}}</t>
+        </is>
+      </c>
+      <c r="D8" s="130" t="n"/>
+      <c r="E8" s="130" t="n"/>
+      <c r="F8" s="130" t="n"/>
+      <c r="G8" s="123" t="n"/>
+      <c r="H8" s="122" t="inlineStr">
         <is>
           <t>검사 시각</t>
         </is>
       </c>
-      <c r="I6" s="46" t="n"/>
-      <c r="J6" s="51" t="inlineStr">
+      <c r="I8" s="123" t="n"/>
+      <c r="J8" s="131" t="inlineStr">
         <is>
           <t>{{target_inspected_at}}</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  {{alert_status}}     회신 기한   ①  {{due_initial}}     ②③  {{due_cause}}     ④  {{due_action}}     ⑤⑥ 「대책서」 2쪽</t>
-        </is>
-      </c>
-      <c r="B7" s="46" t="n"/>
-      <c r="C7" s="46" t="n"/>
-      <c r="D7" s="46" t="n"/>
-      <c r="E7" s="46" t="n"/>
-      <c r="F7" s="46" t="n"/>
-      <c r="G7" s="46" t="n"/>
-      <c r="H7" s="46" t="n"/>
-      <c r="I7" s="46" t="n"/>
-      <c r="J7" s="46" t="n"/>
-      <c r="K7" s="46" t="n"/>
-      <c r="L7" s="46" t="n"/>
-    </row>
-    <row r="8" ht="8" customHeight="1">
-      <c r="A8" s="52" t="n"/>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52" t="n"/>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
-      <c r="K8" s="52" t="n"/>
-      <c r="L8" s="52" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="53" t="inlineStr">
-        <is>
-          <t>불량 현황  |  발행 시점과 대책 적용 후 비교</t>
-        </is>
-      </c>
-      <c r="B9" s="54" t="n"/>
-      <c r="C9" s="54" t="n"/>
-      <c r="D9" s="54" t="n"/>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="54" t="n"/>
-      <c r="G9" s="54" t="n"/>
-      <c r="H9" s="54" t="n"/>
-      <c r="I9" s="54" t="n"/>
-      <c r="J9" s="54" t="n"/>
-      <c r="K9" s="54" t="n"/>
-      <c r="L9" s="54" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="K8" s="130" t="n"/>
+      <c r="L8" s="123" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="137" t="inlineStr">
+        <is>
+          <t>상태 {{alert_status}} · 발행 기준 {{vs_threshold_ratio}}
+회신 ① {{due_initial}}   ②③ {{due_cause}}   ④ {{due_action}}   ⑤⑥ {{due_verify}}</t>
+        </is>
+      </c>
+      <c r="B9" s="133" t="n"/>
+      <c r="C9" s="133" t="n"/>
+      <c r="D9" s="133" t="n"/>
+      <c r="E9" s="133" t="n"/>
+      <c r="F9" s="133" t="n"/>
+      <c r="G9" s="133" t="n"/>
+      <c r="H9" s="133" t="n"/>
+      <c r="I9" s="133" t="n"/>
+      <c r="J9" s="133" t="n"/>
+      <c r="K9" s="133" t="n"/>
+      <c r="L9" s="134" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="122" t="inlineStr">
+        <is>
+          <t>부품 검사 수량</t>
+        </is>
+      </c>
+      <c r="B11" s="130" t="n"/>
+      <c r="C11" s="123" t="n"/>
+      <c r="D11" s="122" t="inlineStr">
+        <is>
+          <t>불량 건수</t>
+        </is>
+      </c>
+      <c r="E11" s="130" t="n"/>
+      <c r="F11" s="123" t="n"/>
+      <c r="G11" s="122" t="inlineStr">
+        <is>
+          <t>발행 PPM</t>
+        </is>
+      </c>
+      <c r="H11" s="130" t="n"/>
+      <c r="I11" s="123" t="n"/>
+      <c r="J11" s="122" t="inlineStr">
+        <is>
+          <t>검증 PPM(계산)</t>
+        </is>
+      </c>
+      <c r="K11" s="130" t="n"/>
+      <c r="L11" s="123" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="138" t="inlineStr">
+        <is>
+          <t>{{inspected_quantity}}</t>
+        </is>
+      </c>
+      <c r="B12" s="130" t="n"/>
+      <c r="C12" s="123" t="n"/>
+      <c r="D12" s="138" t="inlineStr">
+        <is>
+          <t>{{defective_quantity}}</t>
+        </is>
+      </c>
+      <c r="E12" s="130" t="n"/>
+      <c r="F12" s="123" t="n"/>
+      <c r="G12" s="138" t="inlineStr">
+        <is>
+          <t>{{defect_ppm}}</t>
+        </is>
+      </c>
+      <c r="H12" s="130" t="n"/>
+      <c r="I12" s="123" t="n"/>
+      <c r="J12" s="139">
+        <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),I25/G25*1000000,"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="140" t="n"/>
+      <c r="L12" s="141" t="n"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="122" t="inlineStr">
+        <is>
+          <t>집계 기간</t>
+        </is>
+      </c>
+      <c r="B13" s="123" t="n"/>
+      <c r="C13" s="142" t="inlineStr">
+        <is>
+          <t>{{period_start}}
+~ {{period_end}} ({{evaluation_mode}})</t>
+        </is>
+      </c>
+      <c r="D13" s="130" t="n"/>
+      <c r="E13" s="130" t="n"/>
+      <c r="F13" s="130" t="n"/>
+      <c r="G13" s="123" t="n"/>
+      <c r="H13" s="122" t="inlineStr">
+        <is>
+          <t>레시피</t>
+        </is>
+      </c>
+      <c r="I13" s="123" t="n"/>
+      <c r="J13" s="142" t="inlineStr">
+        <is>
+          <t>{{source_recipe_version}}</t>
+        </is>
+      </c>
+      <c r="K13" s="130" t="n"/>
+      <c r="L13" s="123" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="122" t="inlineStr">
+        <is>
+          <t>발생 위치</t>
+        </is>
+      </c>
+      <c r="B14" s="123" t="n"/>
+      <c r="C14" s="131" t="inlineStr">
+        <is>
+          <t>{{target_slot_code}} (발행 대상)
+전체 분포: 불량 근거</t>
+        </is>
+      </c>
+      <c r="D14" s="130" t="n"/>
+      <c r="E14" s="130" t="n"/>
+      <c r="F14" s="123" t="n"/>
+      <c r="G14" s="122" t="inlineStr">
+        <is>
+          <t>완제품 영향</t>
+        </is>
+      </c>
+      <c r="H14" s="123" t="n"/>
+      <c r="I14" s="131" t="inlineStr">
+        <is>
+          <t>{{unit_impact}}</t>
+        </is>
+      </c>
+      <c r="J14" s="130" t="n"/>
+      <c r="K14" s="130" t="n"/>
+      <c r="L14" s="123" t="n"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="122" t="inlineStr">
+        <is>
+          <t>자동 분석</t>
+        </is>
+      </c>
+      <c r="B15" s="123" t="n"/>
+      <c r="C15" s="131" t="inlineStr">
+        <is>
+          <t>{{auto_analysis}}</t>
+        </is>
+      </c>
+      <c r="D15" s="130" t="n"/>
+      <c r="E15" s="130" t="n"/>
+      <c r="F15" s="130" t="n"/>
+      <c r="G15" s="130" t="n"/>
+      <c r="H15" s="130" t="n"/>
+      <c r="I15" s="130" t="n"/>
+      <c r="J15" s="130" t="n"/>
+      <c r="K15" s="130" t="n"/>
+      <c r="L15" s="123" t="n"/>
+    </row>
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="143" t="inlineStr">
+        <is>
+          <t>관리자 직접 작성  |  ①~⑥ 조치·원인·대책·검증·종결</t>
+        </is>
+      </c>
+      <c r="B17" s="130" t="n"/>
+      <c r="C17" s="130" t="n"/>
+      <c r="D17" s="130" t="n"/>
+      <c r="E17" s="130" t="n"/>
+      <c r="F17" s="130" t="n"/>
+      <c r="G17" s="130" t="n"/>
+      <c r="H17" s="130" t="n"/>
+      <c r="I17" s="130" t="n"/>
+      <c r="J17" s="130" t="n"/>
+      <c r="K17" s="130" t="n"/>
+      <c r="L17" s="123" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="122" t="inlineStr">
+        <is>
+          <t>① 초동 조치</t>
+        </is>
+      </c>
+      <c r="B18" s="144" t="n"/>
+      <c r="C18" s="145" t="inlineStr">
+        <is>
+          <t>□ 생산 중단    □ 출하 보류    □ 재고 선별    □ 고객 통보    □ 설비 정지</t>
+        </is>
+      </c>
+      <c r="D18" s="133" t="n"/>
+      <c r="E18" s="133" t="n"/>
+      <c r="F18" s="133" t="n"/>
+      <c r="G18" s="133" t="n"/>
+      <c r="H18" s="133" t="n"/>
+      <c r="I18" s="133" t="n"/>
+      <c r="J18" s="133" t="n"/>
+      <c r="K18" s="133" t="n"/>
+      <c r="L18" s="134" t="n"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="146" t="n"/>
+      <c r="B19" s="147" t="n"/>
+      <c r="C19" s="132" t="n"/>
+      <c r="D19" s="133" t="n"/>
+      <c r="E19" s="133" t="n"/>
+      <c r="F19" s="133" t="n"/>
+      <c r="G19" s="133" t="n"/>
+      <c r="H19" s="133" t="n"/>
+      <c r="I19" s="133" t="n"/>
+      <c r="J19" s="133" t="n"/>
+      <c r="K19" s="133" t="n"/>
+      <c r="L19" s="134" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="122" t="inlineStr">
+        <is>
+          <t>② 발생 원인</t>
+        </is>
+      </c>
+      <c r="B20" s="144" t="n"/>
+      <c r="C20" s="148" t="n"/>
+      <c r="D20" s="133" t="n"/>
+      <c r="E20" s="133" t="n"/>
+      <c r="F20" s="133" t="n"/>
+      <c r="G20" s="133" t="n"/>
+      <c r="H20" s="133" t="n"/>
+      <c r="I20" s="133" t="n"/>
+      <c r="J20" s="133" t="n"/>
+      <c r="K20" s="133" t="n"/>
+      <c r="L20" s="134" t="n"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="146" t="n"/>
+      <c r="B21" s="147" t="n"/>
+      <c r="C21" s="132" t="n"/>
+      <c r="D21" s="133" t="n"/>
+      <c r="E21" s="133" t="n"/>
+      <c r="F21" s="133" t="n"/>
+      <c r="G21" s="133" t="n"/>
+      <c r="H21" s="133" t="n"/>
+      <c r="I21" s="133" t="n"/>
+      <c r="J21" s="133" t="n"/>
+      <c r="K21" s="133" t="n"/>
+      <c r="L21" s="134" t="n"/>
+    </row>
+    <row r="22" ht="53" customHeight="1">
+      <c r="A22" s="122" t="inlineStr">
+        <is>
+          <t>③ 유출 원인</t>
+        </is>
+      </c>
+      <c r="B22" s="123" t="n"/>
+      <c r="C22" s="132" t="n"/>
+      <c r="D22" s="133" t="n"/>
+      <c r="E22" s="133" t="n"/>
+      <c r="F22" s="133" t="n"/>
+      <c r="G22" s="133" t="n"/>
+      <c r="H22" s="133" t="n"/>
+      <c r="I22" s="133" t="n"/>
+      <c r="J22" s="133" t="n"/>
+      <c r="K22" s="133" t="n"/>
+      <c r="L22" s="134" t="n"/>
+    </row>
+    <row r="23" ht="55" customHeight="1">
+      <c r="A23" s="122" t="inlineStr">
+        <is>
+          <t>④ 재발방지
+대책</t>
+        </is>
+      </c>
+      <c r="B23" s="123" t="n"/>
+      <c r="C23" s="132" t="n"/>
+      <c r="D23" s="133" t="n"/>
+      <c r="E23" s="133" t="n"/>
+      <c r="F23" s="133" t="n"/>
+      <c r="G23" s="133" t="n"/>
+      <c r="H23" s="133" t="n"/>
+      <c r="I23" s="133" t="n"/>
+      <c r="J23" s="133" t="n"/>
+      <c r="K23" s="133" t="n"/>
+      <c r="L23" s="134" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="122" t="inlineStr">
+        <is>
+          <t>⑤ 효과 검증</t>
+        </is>
+      </c>
+      <c r="B24" s="144" t="n"/>
+      <c r="C24" s="122" t="inlineStr">
+        <is>
+          <t>검증 기간</t>
+        </is>
+      </c>
+      <c r="D24" s="123" t="n"/>
+      <c r="E24" s="122" t="inlineStr">
+        <is>
+          <t>적용 레시피</t>
+        </is>
+      </c>
+      <c r="F24" s="123" t="n"/>
+      <c r="G24" s="122" t="inlineStr">
         <is>
           <t>검사 수량</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n"/>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="H24" s="123" t="n"/>
+      <c r="I24" s="122" t="inlineStr">
         <is>
           <t>불량 수량</t>
         </is>
       </c>
-      <c r="E10" s="46" t="n"/>
-      <c r="F10" s="46" t="n"/>
-      <c r="G10" s="49" t="inlineStr">
-        <is>
-          <t>발행 시점 PPM</t>
-        </is>
-      </c>
-      <c r="H10" s="46" t="n"/>
-      <c r="I10" s="46" t="n"/>
-      <c r="J10" s="49" t="inlineStr">
-        <is>
-          <t>검증 PPM</t>
-        </is>
-      </c>
-      <c r="K10" s="46" t="n"/>
-      <c r="L10" s="46" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="55" t="inlineStr">
-        <is>
-          <t>{{inspected_quantity}}</t>
-        </is>
-      </c>
-      <c r="B11" s="46" t="n"/>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="55" t="inlineStr">
-        <is>
-          <t>{{defective_quantity}}</t>
-        </is>
-      </c>
-      <c r="E11" s="46" t="n"/>
-      <c r="F11" s="46" t="n"/>
-      <c r="G11" s="55" t="inlineStr">
-        <is>
-          <t>{{defect_ppm}}</t>
-        </is>
-      </c>
-      <c r="H11" s="46" t="n"/>
-      <c r="I11" s="46" t="n"/>
-      <c r="J11" s="55">
-        <f>IF(AND(ISNUMBER(F34),ISNUMBER(H34),F34&gt;0),H34/F34*1000000,"")</f>
+      <c r="J24" s="123" t="n"/>
+      <c r="K24" s="122" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="L24" s="123" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="149" t="n"/>
+      <c r="B25" s="150" t="n"/>
+      <c r="C25" s="151" t="n"/>
+      <c r="D25" s="134" t="n"/>
+      <c r="E25" s="151" t="n"/>
+      <c r="F25" s="134" t="n"/>
+      <c r="G25" s="152" t="n"/>
+      <c r="H25" s="134" t="n"/>
+      <c r="I25" s="152" t="n"/>
+      <c r="J25" s="134" t="n"/>
+      <c r="K25" s="151" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L25" s="134" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="149" t="n"/>
+      <c r="B26" s="150" t="n"/>
+      <c r="C26" s="122" t="inlineStr">
+        <is>
+          <t>불량률(자동 계산)</t>
+        </is>
+      </c>
+      <c r="D26" s="130" t="n"/>
+      <c r="E26" s="123" t="n"/>
+      <c r="F26" s="153">
+        <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),I25/G25,"")</f>
         <v/>
       </c>
-      <c r="K11" s="46" t="n"/>
-      <c r="L11" s="46" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="49" t="inlineStr">
-        <is>
-          <t>집계 기간</t>
-        </is>
-      </c>
-      <c r="B12" s="46" t="n"/>
-      <c r="C12" s="51" t="inlineStr">
-        <is>
-          <t>{{period_start}} ~ {{period_end}} ({{window_days}}일 / {{evaluation_mode}})</t>
-        </is>
-      </c>
-      <c r="H12" s="49" t="inlineStr">
-        <is>
-          <t>레시피</t>
-        </is>
-      </c>
-      <c r="I12" s="46" t="n"/>
-      <c r="J12" s="51" t="inlineStr">
-        <is>
-          <t>{{source_recipe_version}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="49" t="inlineStr">
-        <is>
-          <t>발생 위치</t>
-        </is>
-      </c>
-      <c r="B13" s="46" t="n"/>
-      <c r="C13" s="51" t="inlineStr">
-        <is>
-          <t>{{hotspot}}</t>
-        </is>
-      </c>
-      <c r="H13" s="49" t="inlineStr">
-        <is>
-          <t>발행 기준</t>
-        </is>
-      </c>
-      <c r="I13" s="46" t="n"/>
-      <c r="J13" s="51" t="inlineStr">
-        <is>
-          <t>{{vs_threshold_ratio}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="49" t="inlineStr">
-        <is>
-          <t>완제품 영향</t>
-        </is>
-      </c>
-      <c r="B14" s="46" t="n"/>
-      <c r="C14" s="51" t="inlineStr">
-        <is>
-          <t>{{unit_impact}}</t>
-        </is>
-      </c>
-      <c r="F14" s="49" t="inlineStr">
-        <is>
-          <t>제조사 P/N</t>
-        </is>
-      </c>
-      <c r="G14" s="46" t="n"/>
-      <c r="H14" s="56" t="inlineStr">
-        <is>
-          <t>{{datasheet_match}} · {{selected_mpn}}
-정격 {{selected_spec}} · 공급사 {{selected_supplier}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="49" t="inlineStr">
-        <is>
-          <t>자동 분석</t>
-        </is>
-      </c>
-      <c r="B15" s="46" t="n"/>
-      <c r="C15" s="57" t="inlineStr">
-        <is>
-          <t>{{auto_analysis}}</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="n"/>
-      <c r="E15" s="46" t="n"/>
-      <c r="F15" s="46" t="n"/>
-      <c r="G15" s="46" t="n"/>
-      <c r="H15" s="46" t="n"/>
-      <c r="I15" s="46" t="n"/>
-      <c r="J15" s="46" t="n"/>
-      <c r="K15" s="46" t="n"/>
-      <c r="L15" s="46" t="n"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="49" t="inlineStr">
-        <is>
-          <t>핵심 원인</t>
-        </is>
-      </c>
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="58" t="n"/>
-      <c r="D16" s="59" t="n"/>
-      <c r="E16" s="59" t="n"/>
-      <c r="F16" s="59" t="n"/>
-      <c r="G16" s="59" t="n"/>
-      <c r="H16" s="59" t="n"/>
-      <c r="I16" s="59" t="n"/>
-      <c r="J16" s="59" t="n"/>
-      <c r="K16" s="59" t="n"/>
-      <c r="L16" s="59" t="n"/>
-    </row>
-    <row r="17" ht="8" customHeight="1">
-      <c r="A17" s="52" t="n"/>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="52" t="n"/>
-      <c r="K17" s="52" t="n"/>
-      <c r="L17" s="52" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
-        <is>
-          <t>① 초동 조치  |  확산 방지와 영향 범위</t>
-        </is>
-      </c>
-      <c r="B18" s="54" t="n"/>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="54" t="n"/>
-      <c r="E18" s="54" t="n"/>
-      <c r="F18" s="54" t="n"/>
-      <c r="G18" s="54" t="n"/>
-      <c r="H18" s="54" t="n"/>
-      <c r="I18" s="54" t="n"/>
-      <c r="J18" s="54" t="n"/>
-      <c r="K18" s="54" t="n"/>
-      <c r="L18" s="54" t="n"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="60" t="inlineStr">
-        <is>
-          <t>협조 필요    ☐ 생산 중단    ☐ 출하 보류    ☐ 재고 선별    ☐ 고객 통보    ☐ 설비 정지</t>
-        </is>
-      </c>
-      <c r="B19" s="59" t="n"/>
-      <c r="C19" s="59" t="n"/>
-      <c r="D19" s="59" t="n"/>
-      <c r="E19" s="59" t="n"/>
-      <c r="F19" s="59" t="n"/>
-      <c r="G19" s="59" t="n"/>
-      <c r="H19" s="59" t="n"/>
-      <c r="I19" s="59" t="n"/>
-      <c r="J19" s="59" t="n"/>
-      <c r="K19" s="59" t="n"/>
-      <c r="L19" s="59" t="n"/>
-    </row>
-    <row r="20" ht="100" customHeight="1">
-      <c r="A20" s="61" t="n"/>
-      <c r="B20" s="59" t="n"/>
-      <c r="C20" s="59" t="n"/>
-      <c r="D20" s="59" t="n"/>
-      <c r="E20" s="59" t="n"/>
-      <c r="F20" s="59" t="n"/>
-      <c r="G20" s="59" t="n"/>
-      <c r="H20" s="59" t="n"/>
-      <c r="I20" s="59" t="n"/>
-      <c r="J20" s="59" t="n"/>
-      <c r="K20" s="59" t="n"/>
-      <c r="L20" s="59" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="49" t="inlineStr">
-        <is>
-          <t>대책 요약</t>
-        </is>
-      </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="62" t="n"/>
-      <c r="D21" s="59" t="n"/>
-      <c r="E21" s="59" t="n"/>
-      <c r="F21" s="59" t="n"/>
-      <c r="G21" s="59" t="n"/>
-      <c r="H21" s="59" t="n"/>
-      <c r="I21" s="59" t="n"/>
-      <c r="J21" s="59" t="n"/>
-      <c r="K21" s="59" t="n"/>
-      <c r="L21" s="59" t="n"/>
-    </row>
-    <row r="22" ht="50" customHeight="1">
-      <c r="A22" s="46" t="n"/>
-      <c r="B22" s="46" t="n"/>
-      <c r="C22" s="59" t="n"/>
-      <c r="D22" s="59" t="n"/>
-      <c r="E22" s="59" t="n"/>
-      <c r="F22" s="59" t="n"/>
-      <c r="G22" s="59" t="n"/>
-      <c r="H22" s="59" t="n"/>
-      <c r="I22" s="59" t="n"/>
-      <c r="J22" s="59" t="n"/>
-      <c r="K22" s="59" t="n"/>
-      <c r="L22" s="59" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="63" t="inlineStr">
-        <is>
-          <t>작성 안내: 연노랑은 담당자 입력 · 파랑은 현황/계산 · 상세 원인부터 종결까지 다음 페이지에 이어집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="53" t="inlineStr">
-        <is>
-          <t>불량 대책서  |  원인 · 대책 · 검증 · 종결</t>
-        </is>
-      </c>
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="54" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-      <c r="H24" s="54" t="n"/>
-      <c r="I24" s="54" t="n"/>
-      <c r="J24" s="54" t="n"/>
-      <c r="K24" s="54" t="n"/>
-      <c r="L24" s="54" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="47">
-        <f>C3&amp;"  ·  "&amp;C4&amp;"  /  "&amp;J4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="53" t="inlineStr">
-        <is>
-          <t>② 발생 원인  |  재현·실물 확인 근거</t>
-        </is>
-      </c>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="54" t="n"/>
-      <c r="I26" s="54" t="n"/>
-      <c r="J26" s="54" t="n"/>
-      <c r="K26" s="54" t="n"/>
-      <c r="L26" s="54" t="n"/>
-    </row>
-    <row r="27" ht="84" customHeight="1">
-      <c r="A27" s="61" t="n"/>
-      <c r="B27" s="59" t="n"/>
-      <c r="C27" s="59" t="n"/>
-      <c r="D27" s="59" t="n"/>
-      <c r="E27" s="59" t="n"/>
-      <c r="F27" s="59" t="n"/>
-      <c r="G27" s="59" t="n"/>
-      <c r="H27" s="59" t="n"/>
-      <c r="I27" s="59" t="n"/>
-      <c r="J27" s="59" t="n"/>
-      <c r="K27" s="59" t="n"/>
-      <c r="L27" s="59" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t>③ 유출 원인  |  검사·판정 기준의 한계</t>
-        </is>
-      </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="54" t="n"/>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="54" t="n"/>
-      <c r="I28" s="54" t="n"/>
-      <c r="J28" s="54" t="n"/>
-      <c r="K28" s="54" t="n"/>
-      <c r="L28" s="54" t="n"/>
-    </row>
-    <row r="29" ht="70" customHeight="1">
-      <c r="A29" s="61" t="n"/>
-      <c r="B29" s="59" t="n"/>
-      <c r="C29" s="59" t="n"/>
-      <c r="D29" s="59" t="n"/>
-      <c r="E29" s="59" t="n"/>
-      <c r="F29" s="59" t="n"/>
-      <c r="G29" s="59" t="n"/>
-      <c r="H29" s="59" t="n"/>
-      <c r="I29" s="59" t="n"/>
-      <c r="J29" s="59" t="n"/>
-      <c r="K29" s="59" t="n"/>
-      <c r="L29" s="59" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="53" t="inlineStr">
-        <is>
-          <t>④ 재발방지 대책  |  적용 내용 · 담당 · 일정 · 수평전개</t>
-        </is>
-      </c>
-      <c r="B30" s="54" t="n"/>
-      <c r="C30" s="54" t="n"/>
-      <c r="D30" s="54" t="n"/>
-      <c r="E30" s="54" t="n"/>
-      <c r="F30" s="54" t="n"/>
-      <c r="G30" s="54" t="n"/>
-      <c r="H30" s="54" t="n"/>
-      <c r="I30" s="54" t="n"/>
-      <c r="J30" s="54" t="n"/>
-      <c r="K30" s="54" t="n"/>
-      <c r="L30" s="54" t="n"/>
-    </row>
-    <row r="31" ht="84" customHeight="1">
-      <c r="A31" s="61" t="n"/>
-      <c r="B31" s="59" t="n"/>
-      <c r="C31" s="59" t="n"/>
-      <c r="D31" s="59" t="n"/>
-      <c r="E31" s="59" t="n"/>
-      <c r="F31" s="59" t="n"/>
-      <c r="G31" s="59" t="n"/>
-      <c r="H31" s="59" t="n"/>
-      <c r="I31" s="59" t="n"/>
-      <c r="J31" s="59" t="n"/>
-      <c r="K31" s="59" t="n"/>
-      <c r="L31" s="59" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="53" t="inlineStr">
-        <is>
-          <t>⑤ 효과 검증  |  {{due_verify}}</t>
-        </is>
-      </c>
-      <c r="B32" s="54" t="n"/>
-      <c r="C32" s="54" t="n"/>
-      <c r="D32" s="54" t="n"/>
-      <c r="E32" s="54" t="n"/>
-      <c r="F32" s="54" t="n"/>
-      <c r="G32" s="54" t="n"/>
-      <c r="H32" s="54" t="n"/>
-      <c r="I32" s="54" t="n"/>
-      <c r="J32" s="54" t="n"/>
-      <c r="K32" s="54" t="n"/>
-      <c r="L32" s="54" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="49" t="inlineStr">
-        <is>
-          <t>검증 기간</t>
-        </is>
-      </c>
-      <c r="B33" s="46" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="49" t="inlineStr">
-        <is>
-          <t>적용 레시피</t>
-        </is>
-      </c>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="49" t="inlineStr">
-        <is>
-          <t>검사 수량</t>
-        </is>
-      </c>
-      <c r="G33" s="46" t="n"/>
-      <c r="H33" s="49" t="inlineStr">
-        <is>
-          <t>불량 수량</t>
-        </is>
-      </c>
-      <c r="I33" s="46" t="n"/>
-      <c r="J33" s="49" t="inlineStr">
-        <is>
-          <t>판정</t>
-        </is>
-      </c>
-      <c r="K33" s="46" t="n"/>
-      <c r="L33" s="46" t="n"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="64" t="n"/>
-      <c r="B34" s="59" t="n"/>
-      <c r="C34" s="59" t="n"/>
-      <c r="D34" s="64" t="n"/>
-      <c r="E34" s="59" t="n"/>
-      <c r="F34" s="65" t="n"/>
-      <c r="G34" s="59" t="n"/>
-      <c r="H34" s="65" t="n"/>
-      <c r="I34" s="59" t="n"/>
-      <c r="J34" s="64" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="K34" s="59" t="n"/>
-      <c r="L34" s="59" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="49" t="inlineStr">
-        <is>
-          <t>검증 불량률</t>
-        </is>
-      </c>
-      <c r="B35" s="46" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="66">
-        <f>IF(AND(ISNUMBER(F34),ISNUMBER(H34),F34&gt;0),H34/F34,"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="46" t="n"/>
-      <c r="F35" s="47" t="inlineStr">
-        <is>
-          <t>판정 근거는 아래에 작성합니다. 수량은 부품 검사 건수 기준입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="61" t="n"/>
-      <c r="B36" s="59" t="n"/>
-      <c r="C36" s="59" t="n"/>
-      <c r="D36" s="59" t="n"/>
-      <c r="E36" s="59" t="n"/>
-      <c r="F36" s="59" t="n"/>
-      <c r="G36" s="59" t="n"/>
-      <c r="H36" s="59" t="n"/>
-      <c r="I36" s="59" t="n"/>
-      <c r="J36" s="59" t="n"/>
-      <c r="K36" s="59" t="n"/>
-      <c r="L36" s="59" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="53" t="inlineStr">
-        <is>
-          <t>⑥ 종결 판정</t>
-        </is>
-      </c>
-      <c r="B37" s="54" t="n"/>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="F37" s="54" t="n"/>
-      <c r="G37" s="54" t="n"/>
-      <c r="H37" s="54" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="54" t="n"/>
-      <c r="K37" s="54" t="n"/>
-      <c r="L37" s="54" t="n"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="49" t="inlineStr">
+      <c r="G26" s="141" t="n"/>
+      <c r="H26" s="136" t="inlineStr">
+        <is>
+          <t>검증 수량: 부품 검사 건수 기준</t>
+        </is>
+      </c>
+      <c r="I26" s="130" t="n"/>
+      <c r="J26" s="130" t="n"/>
+      <c r="K26" s="130" t="n"/>
+      <c r="L26" s="123" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="146" t="n"/>
+      <c r="B27" s="147" t="n"/>
+      <c r="C27" s="132" t="n"/>
+      <c r="D27" s="133" t="n"/>
+      <c r="E27" s="133" t="n"/>
+      <c r="F27" s="133" t="n"/>
+      <c r="G27" s="133" t="n"/>
+      <c r="H27" s="133" t="n"/>
+      <c r="I27" s="133" t="n"/>
+      <c r="J27" s="133" t="n"/>
+      <c r="K27" s="133" t="n"/>
+      <c r="L27" s="134" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="122" t="inlineStr">
+        <is>
+          <t>⑥ 종결</t>
+        </is>
+      </c>
+      <c r="B28" s="144" t="n"/>
+      <c r="C28" s="122" t="inlineStr">
         <is>
           <t>종결일</t>
         </is>
       </c>
-      <c r="B38" s="46" t="n"/>
-      <c r="C38" s="62" t="n"/>
-      <c r="D38" s="59" t="n"/>
-      <c r="E38" s="59" t="n"/>
-      <c r="F38" s="59" t="n"/>
-      <c r="G38" s="47" t="inlineStr">
-        <is>
-          <t>잔여 위험과 이관 사항을 종결 의견에 기록</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="56" customHeight="1">
-      <c r="A39" s="61" t="n"/>
-      <c r="B39" s="59" t="n"/>
-      <c r="C39" s="59" t="n"/>
-      <c r="D39" s="59" t="n"/>
-      <c r="E39" s="59" t="n"/>
-      <c r="F39" s="59" t="n"/>
-      <c r="G39" s="59" t="n"/>
-      <c r="H39" s="59" t="n"/>
-      <c r="I39" s="59" t="n"/>
-      <c r="J39" s="59" t="n"/>
-      <c r="K39" s="59" t="n"/>
-      <c r="L39" s="59" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="49" t="inlineStr">
-        <is>
-          <t>작성</t>
-        </is>
-      </c>
-      <c r="B40" s="46" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
-      <c r="E40" s="49" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="F40" s="46" t="n"/>
-      <c r="G40" s="46" t="n"/>
-      <c r="H40" s="46" t="n"/>
-      <c r="I40" s="49" t="inlineStr">
-        <is>
-          <t>승인</t>
-        </is>
-      </c>
-      <c r="J40" s="46" t="n"/>
-      <c r="K40" s="46" t="n"/>
-      <c r="L40" s="46" t="n"/>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="62" t="n"/>
-      <c r="B41" s="59" t="n"/>
-      <c r="C41" s="59" t="n"/>
-      <c r="D41" s="59" t="n"/>
-      <c r="E41" s="62" t="n"/>
-      <c r="F41" s="59" t="n"/>
-      <c r="G41" s="59" t="n"/>
-      <c r="H41" s="59" t="n"/>
-      <c r="I41" s="62" t="n"/>
-      <c r="J41" s="59" t="n"/>
-      <c r="K41" s="59" t="n"/>
-      <c r="L41" s="59" t="n"/>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="67" t="inlineStr">
-        <is>
-          <t>검토용 v2 · 자동 발행 시스템 채택 전 검토본 · 입력 칸을 클릭하면 작성 요령을 볼 수 있습니다.</t>
+      <c r="D28" s="123" t="n"/>
+      <c r="E28" s="132" t="n"/>
+      <c r="F28" s="133" t="n"/>
+      <c r="G28" s="134" t="n"/>
+      <c r="H28" s="154" t="inlineStr">
+        <is>
+          <t>잔여 위험 · 이관 사항 확인</t>
+        </is>
+      </c>
+      <c r="I28" s="130" t="n"/>
+      <c r="J28" s="130" t="n"/>
+      <c r="K28" s="130" t="n"/>
+      <c r="L28" s="123" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="146" t="n"/>
+      <c r="B29" s="147" t="n"/>
+      <c r="C29" s="132" t="n"/>
+      <c r="D29" s="133" t="n"/>
+      <c r="E29" s="133" t="n"/>
+      <c r="F29" s="133" t="n"/>
+      <c r="G29" s="133" t="n"/>
+      <c r="H29" s="133" t="n"/>
+      <c r="I29" s="133" t="n"/>
+      <c r="J29" s="133" t="n"/>
+      <c r="K29" s="133" t="n"/>
+      <c r="L29" s="134" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="155" t="inlineStr">
+        <is>
+          <t>노랑: 관리자 작성 · 파랑: 자동 계산 · 그 외: 시스템 기입 / 입력 칸 클릭 시 작성 안내</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="87">
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="75">
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="I14:L14"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="H26:L26"/>
+    <mergeCell ref="K2:L3"/>
     <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A28:B29"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="G2:H3"/>
+    <mergeCell ref="A24:B27"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="H28:L28"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="J13:L13"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A1:F3"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="G38:L38"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="C21:L22"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="F35:L35"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J34:L34">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+  <conditionalFormatting sqref="K25:L25">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"EFFECTIVE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
       <formula>"INEFFECTIVE"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="5">
       <formula>"PENDING"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="17">
-    <dataValidation sqref="J4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="참고 시트 2개은 유형과 무관하게 항상 첨부한다.&#10;어느 자료가 이번 건에 쓸모 있는지는 담당자가 판단한다." type="list">
+  <dataValidations count="18">
+    <dataValidation sqref="J6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="참고 시트 2개은 유형과 무관하게 항상 첨부한다.&#10;어느 자료가 이번 건에 쓸모 있는지는 담당자가 판단한다." type="list">
       <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
     </dataValidation>
-    <dataValidation sqref="A19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 ☐ 를 ☑ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;"/>
-    <dataValidation sqref="A20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;"/>
-    <dataValidation sqref="C16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 한 줄 요약 (40자)" prompt="아래 본문을 한 줄로 줄인 것. 예: '배치 하강속도 상향 + 지지 핀 최원거리 슬롯'&#10;본문은 길어서 이 칸에 들어가지 않으므로 핵심 원인만 적는다."/>
-    <dataValidation sqref="A27" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「불량 근거」의 발생 기록과 검사 이미지를 확인한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;"/>
-    <dataValidation sqref="A29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「부품 검토자료」의 데이터시트 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;"/>
-    <dataValidation sqref="A31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「부품 검토자료」의 대체품 영역의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;"/>
-    <dataValidation sqref="A34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;"/>
-    <dataValidation sqref="D34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;"/>
-    <dataValidation sqref="F34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;"/>
-    <dataValidation sqref="H34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt=""/>
-    <dataValidation sqref="J34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="품질 절차에서 정한 판정 기준에 따라 선택한다." type="list">
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 □ 를 ■ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;"/>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;"/>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 한 줄 요약 (40자)" prompt="본문을 한 줄로 줄인 것. 예: '배치 하강속도 상향 + 지지 핀 최원거리 슬롯'&#10;본문은 길어서 이 칸에 들어가지 않으므로 핵심 원인만 적는다."/>
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「불량 근거」의 발생 기록과 검사 이미지를 확인한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;"/>
+    <dataValidation sqref="C22" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「부품 검토자료」의 데이터시트 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;"/>
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「부품 검토자료」의 대체품 영역의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;"/>
+    <dataValidation sqref="C25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;"/>
+    <dataValidation sqref="E25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;"/>
+    <dataValidation sqref="G25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;"/>
+    <dataValidation sqref="G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt=""/>
+    <dataValidation sqref="I25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="품질 절차에서 정한 판정 기준에 따라 선택한다." type="list">
       <formula1>"PENDING,EFFECTIVE,INEFFECTIVE"</formula1>
     </dataValidation>
-    <dataValidation sqref="J34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="판정 기준과 비교한 결론을 선택한다.&#10;기준은 해당 품질 절차에서 확인한다."/>
-    <dataValidation sqref="A36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;"/>
-    <dataValidation sqref="C38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt=""/>
-    <dataValidation sqref="A39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;"/>
-    <dataValidation sqref="F34 H34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
+    <dataValidation sqref="K25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="판정 기준과 비교한 결론을 선택한다.&#10;기준은 해당 품질 절차에서 확인한다."/>
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;"/>
+    <dataValidation sqref="E28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt=""/>
+    <dataValidation sqref="C29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.32" right="0.32" top="0.35" bottom="0.38" header="0.15" footer="0.17"/>
+  <pageMargins left="0.32" right="0.32" top="0.32" bottom="0.32" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 검토용&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="23" min="0" max="16383" man="1"/>
-  </rowBreaks>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -2163,21 +2543,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
-        <is>
-          <t>불량 근거  |  발행 시점 고정</t>
+      <c r="A1" s="156" t="inlineStr">
+        <is>
+          <t>불량 근거 · 시스템 자동 기입 / 발행 시점 고정</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="70" t="inlineStr">
         <is>
           <t>production.unit_defects 확정 기록 · 문서번호 {{alert_code}} · 수정 금지</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>슬롯별 발생 분포        어느 슬롯에 몰려 있는지 · 공정 원인 판단의 1차 근거</t>
         </is>
@@ -2188,45 +2568,45 @@
       <c r="E3" s="30" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="71" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>불량 건수</t>
         </is>
       </c>
-      <c r="C4" s="71" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>슬롯 불량률</t>
         </is>
       </c>
-      <c r="D4" s="71" t="inlineStr">
+      <c r="D4" s="72" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
       <c r="E4" s="30" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="72" t="inlineStr">
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="73" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="B5" s="73" t="inlineStr">
+      <c r="B5" s="74" t="inlineStr">
         <is>
           <t>{{count}}</t>
         </is>
       </c>
-      <c r="C5" s="74" t="inlineStr">
+      <c r="C5" s="75" t="inlineStr">
         <is>
           <t>{{slot_rate}}</t>
         </is>
       </c>
-      <c r="D5" s="75" t="inlineStr">
+      <c r="D5" s="76" t="inlineStr">
         <is>
           <t>{{slot_note}}</t>
         </is>
@@ -2235,7 +2615,7 @@
     </row>
     <row r="6" ht="30" customHeight="1"/>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="71" t="inlineStr">
         <is>
           <t>불량 유닛 목록</t>
         </is>
@@ -2246,54 +2626,54 @@
       <c r="E7" s="30" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="71" t="inlineStr">
+      <c r="A8" s="72" t="inlineStr">
         <is>
           <t>unit_id</t>
         </is>
       </c>
-      <c r="B8" s="71" t="inlineStr">
+      <c r="B8" s="72" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="C8" s="71" t="inlineStr">
+      <c r="C8" s="72" t="inlineStr">
         <is>
           <t>불량 유형</t>
         </is>
       </c>
-      <c r="D8" s="71" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>검사 시각</t>
         </is>
       </c>
-      <c r="E8" s="71" t="inlineStr">
+      <c r="E8" s="72" t="inlineStr">
         <is>
           <t>검사 이미지 경로</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="73" t="inlineStr">
         <is>
           <t>{{unit_id}}</t>
         </is>
       </c>
-      <c r="B9" s="72" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="C9" s="72" t="inlineStr">
+      <c r="C9" s="73" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
       </c>
-      <c r="D9" s="72" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
         <is>
           <t>{{inspected_at}}</t>
         </is>
       </c>
-      <c r="E9" s="75" t="inlineStr">
+      <c r="E9" s="76" t="inlineStr">
         <is>
           <t>{{inspection_image_path}}</t>
         </is>
@@ -2301,7 +2681,7 @@
     </row>
     <row r="10" ht="30" customHeight="1"/>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>검사 이미지</t>
         </is>
@@ -2312,7 +2692,7 @@
       <c r="E11" s="30" t="n"/>
     </row>
     <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="76" t="inlineStr">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>{{inspection_image_status}} · {{inspection_image_path}} · SHA-256 {{inspection_image_sha256}}</t>
         </is>
@@ -2324,33 +2704,33 @@
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="34" t="n"/>
-      <c r="B13" s="77" t="n"/>
-      <c r="C13" s="77" t="n"/>
-      <c r="D13" s="77" t="n"/>
-      <c r="E13" s="78" t="n"/>
+      <c r="B13" s="78" t="n"/>
+      <c r="C13" s="78" t="n"/>
+      <c r="D13" s="78" t="n"/>
+      <c r="E13" s="79" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="79" t="n"/>
-      <c r="E14" s="80" t="n"/>
+      <c r="A14" s="80" t="n"/>
+      <c r="E14" s="81" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="79" t="n"/>
-      <c r="E15" s="80" t="n"/>
+      <c r="A15" s="80" t="n"/>
+      <c r="E15" s="81" t="n"/>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="79" t="n"/>
-      <c r="E16" s="80" t="n"/>
+      <c r="A16" s="80" t="n"/>
+      <c r="E16" s="81" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="79" t="n"/>
-      <c r="E17" s="80" t="n"/>
+      <c r="A17" s="80" t="n"/>
+      <c r="E17" s="81" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="81" t="n"/>
-      <c r="B18" s="82" t="n"/>
-      <c r="C18" s="82" t="n"/>
-      <c r="D18" s="82" t="n"/>
-      <c r="E18" s="83" t="n"/>
+      <c r="A18" s="82" t="n"/>
+      <c r="B18" s="83" t="n"/>
+      <c r="C18" s="83" t="n"/>
+      <c r="D18" s="83" t="n"/>
+      <c r="E18" s="84" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
@@ -2376,6 +2756,7 @@
     <firstFooter/>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2389,23 +2770,23 @@
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="84" t="inlineStr">
-        <is>
-          <t>부품 검토자료</t>
+      <c r="A1" s="157" t="inlineStr">
+        <is>
+          <t>부품 검토자료 · 시스템 자동 기입</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="85" t="inlineStr">
+      <c r="A2" s="86" t="inlineStr">
         <is>
           <t>부품 범주 {{category_label}} · 데이터시트 대조 {{datasheet_match}} · 기준일 {{source_dated_on}} · 조회 {{queried_at}}</t>
         </is>
@@ -2417,11 +2798,6 @@
           <t>현재 부품  |  데이터시트 대조</t>
         </is>
       </c>
-      <c r="B3" s="54" t="n"/>
-      <c r="C3" s="54" t="n"/>
-      <c r="D3" s="54" t="n"/>
-      <c r="E3" s="54" t="n"/>
-      <c r="F3" s="54" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="49" t="inlineStr">
@@ -2439,9 +2815,9 @@
           <t>공급사</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
-        <is>
-          <t>단가</t>
+      <c r="D4" s="158" t="inlineStr">
+        <is>
+          <t>단가(USD)</t>
         </is>
       </c>
       <c r="E4" s="49" t="inlineStr">
@@ -2455,7 +2831,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="50" t="inlineStr">
         <is>
           <t>{{selected_mpn}}</t>
@@ -2471,17 +2847,17 @@
           <t>{{selected_supplier}}</t>
         </is>
       </c>
-      <c r="D5" s="50" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>{{selected_unit_price}}</t>
         </is>
       </c>
-      <c r="E5" s="50" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>{{selected_price_basis}}</t>
         </is>
       </c>
-      <c r="F5" s="50" t="inlineStr">
+      <c r="F5" s="57" t="inlineStr">
         <is>
           <t>{{selected_price_checked_at}}</t>
         </is>
@@ -2498,14 +2874,9 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="53" t="inlineStr">
         <is>
-          <t>품질 체크리스트  |  검사 항목과 이상 시 조치</t>
-        </is>
-      </c>
-      <c r="B7" s="54" t="n"/>
-      <c r="C7" s="54" t="n"/>
-      <c r="D7" s="54" t="n"/>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="54" t="n"/>
+          <t>품질 체크리스트  |  공통 기준 + 부품별 기준</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="49" t="inlineStr">
@@ -2518,65 +2889,57 @@
           <t>확인 항목</t>
         </is>
       </c>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="46" t="n"/>
       <c r="E8" s="49" t="inlineStr">
         <is>
           <t>이상 시 조치</t>
         </is>
       </c>
-      <c r="F8" s="46" t="n"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
+    </row>
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="49" t="inlineStr">
         <is>
           <t>입고 검사</t>
         </is>
       </c>
-      <c r="B9" s="50" t="inlineStr">
+      <c r="B9" s="159" t="inlineStr">
         <is>
           <t>{{incoming_inspection}}</t>
         </is>
       </c>
-      <c r="E9" s="61" t="inlineStr">
+      <c r="E9" s="159" t="inlineStr">
         <is>
           <t>{{action_on_anomaly}}</t>
         </is>
       </c>
-      <c r="F9" s="59" t="n"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
+    </row>
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="49" t="inlineStr">
         <is>
           <t>조립·보관</t>
         </is>
       </c>
-      <c r="B10" s="50" t="inlineStr">
+      <c r="B10" s="159" t="inlineStr">
         <is>
           <t>{{assembly_control}}</t>
         </is>
       </c>
-      <c r="E10" s="59" t="n"/>
-      <c r="F10" s="59" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
+    </row>
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="49" t="inlineStr">
         <is>
           <t>기능·신뢰성</t>
         </is>
       </c>
-      <c r="B11" s="50" t="inlineStr">
+      <c r="B11" s="159" t="inlineStr">
         <is>
           <t>{{reliability_test}}</t>
         </is>
       </c>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="59" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="47" t="inlineStr">
         <is>
-          <t>부품 데이터시트 Checklist 시트에서 조회 · 원인 자동 추정 자료가 아님</t>
+          <t>Checklist 공통·부품별 항목을 함께 조회 · 원인·적합성 판단은 관리자 작성</t>
         </is>
       </c>
     </row>
@@ -2594,28 +2957,18 @@
           <t>대체품 후보  |  적합성 검증·변경 승인 후 적용</t>
         </is>
       </c>
-      <c r="B14" s="54" t="n"/>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="54" t="n"/>
-      <c r="E14" s="54" t="n"/>
-      <c r="F14" s="54" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="86" t="inlineStr">
+      <c r="A15" s="87" t="inlineStr">
         <is>
           <t>같은 부품 타입이라는 것 외에 검증된 것은 없다 · 동일 정격만으로 drop-in 판단 금지 · 핀/패키지/정격/열/수명 재검증과 변경 승인을 거친 뒤에만 적용한다.</t>
         </is>
       </c>
-      <c r="B15" s="87" t="n"/>
-      <c r="C15" s="87" t="n"/>
-      <c r="D15" s="87" t="n"/>
-      <c r="E15" s="87" t="n"/>
-      <c r="F15" s="87" t="n"/>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="85" t="inlineStr">
-        <is>
-          <t>조회 시각 {{queried_at}}   ·   데이터시트 {{source_file}} (기준일 {{source_dated_on}})   ·   부품 타입 {{category_label}}   ·   후보 {{candidate_count}}종   ·   단가 {{price_range}}   ·   현재 선정 {{price_selected}}</t>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="86" t="inlineStr">
+        <is>
+          <t>같은 타입 후보 {{candidate_count}}종 · 단가 {{price_range}} · 현재 선정 {{price_selected}} · 호환성 미승인</t>
         </is>
       </c>
     </row>
@@ -2635,9 +2988,9 @@
           <t>공급사</t>
         </is>
       </c>
-      <c r="D17" s="49" t="inlineStr">
-        <is>
-          <t>단가</t>
+      <c r="D17" s="158" t="inlineStr">
+        <is>
+          <t>단가(USD)</t>
         </is>
       </c>
       <c r="E17" s="49" t="inlineStr">
@@ -2651,77 +3004,77 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="88" t="inlineStr">
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="89" t="inlineStr">
         <is>
           <t>{{manufacturer_part_number}}</t>
         </is>
       </c>
-      <c r="B18" s="88" t="inlineStr">
+      <c r="B18" s="90" t="inlineStr">
         <is>
           <t>{{key_spec}}</t>
         </is>
       </c>
-      <c r="C18" s="88" t="inlineStr">
+      <c r="C18" s="90" t="inlineStr">
         <is>
           <t>{{supplier}}</t>
         </is>
       </c>
-      <c r="D18" s="88" t="inlineStr">
+      <c r="D18" s="90" t="inlineStr">
         <is>
           <t>{{unit_price}}</t>
         </is>
       </c>
-      <c r="E18" s="88" t="inlineStr">
+      <c r="E18" s="90" t="inlineStr">
         <is>
           <t>{{price_basis}}</t>
         </is>
       </c>
-      <c r="F18" s="88" t="inlineStr">
+      <c r="F18" s="90" t="inlineStr">
         <is>
           <t>{{price_checked_at}}</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="52" t="n"/>
-      <c r="B19" s="52" t="n"/>
-      <c r="C19" s="52" t="n"/>
-      <c r="D19" s="52" t="n"/>
-      <c r="E19" s="52" t="n"/>
-      <c r="F19" s="52" t="n"/>
-    </row>
+    <row r="19" ht="50" customHeight="1"/>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="85" t="inlineStr">
-        <is>
-          <t>단가는 데이터시트 기준일의 값이고 발주 근거가 아니다. MOQ·재고·리드타임과 상호호환 판정은 이 문서에 없다 → GET /parts/{{part_id}} 또는 구매·품질 담당</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t>원본 {{source_file}} · DB parts: {{part_id}} / {{part_name}} / {{category_label}} · 데이터시트 MPN 대조: {{datasheet_match}}</t>
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>단가는 데이터시트 기준일의 값이고 발주 근거가 아니다. MOQ·재고·리드타임과 상호호환 판정은 이 문서에 없다 → GET /api/v1/parts/{{part_id}} 또는 구매·품질 담당</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="160" t="inlineStr">
+        <is>
+          <t>원본 {{source_file}}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A2:F2"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="22">
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F11"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="E9:F11"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -2735,5 +3088,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
@@ -27,7 +27,7 @@
     <definedName name="reply_closed_at">'대책서'!$E$28</definedName>
     <definedName name="reply_closure_note">'대책서'!$C$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$L$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'불량 근거'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'불량 근거'!$A$1:$E$23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'부품 검토자료'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -40,7 +40,7 @@
     <numFmt numFmtId="164" formatCode="0.0&quot;배&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="67">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,8 +350,73 @@
       <color rgb="00243D5B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00233D59"/>
+      <sz val="23"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00263442"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00263442"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00263442"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00263442"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00263442"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00657385"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00263442"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00263442"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00233D59"/>
+      <sz val="17"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00263442"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00233D59"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -428,8 +493,28 @@
         <fgColor rgb="00F2F3F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF3F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF5F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -757,11 +842,118 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC6D1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BCC6D1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC6D1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC6D1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC6D1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC6D1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC6D1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BCC6D1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC6D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC6D1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BCC6D1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BCC6D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC6D1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC6D1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BCC6D1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC6D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC6D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BCC6D1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BCC6D1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1186,6 +1378,256 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="58" fillId="17" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="19" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="19" borderId="26" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="19" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="16" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="16" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="16" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="10" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="25" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="19" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="35" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="36" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="19" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="17" borderId="23" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="19" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="19" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="19" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="19" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="19" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1229,33 +1671,18 @@
         <b val="1"/>
         <color rgb="00216348"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00EEF5F0"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
         <color rgb="009C2A2A"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F9EEEE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
         <color rgb="0080601B"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFF9EB"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1341,6 +1768,12 @@
         <t>부품 식별자: {{part_id}}</t>
       </text>
     </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+시스템 자동 기입 · 발행 시점 고정  |  담당·기한·문서 상태는 관리자 갱신</t>
+      </text>
+    </comment>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
         <t>제조사 P/N·정격·공급사 (이전 v2)
@@ -1361,22 +1794,25 @@
     </comment>
     <comment ref="A9" authorId="0" shapeId="0">
       <text>
-        <t>문서 상태와 회신 기한은 시스템이 ISSUED / 담당자 입력으로 초기화하며 이후 관리자가 갱신합니다. Job 상태 또는 DB의 메일 전송 상태와 별개입니다.</t>
+        <t>문서 상태와 회신 기한은 시스템이 ISSUED / 담당자 입력으로 초기화하며 이후 관리자가 갱신합니다. Job 상태 또는 DB의 메일 전송 상태와 별개입니다.
+이전 v2 내용(참고):
+상태 {{alert_status}} · 발행 기준 {{vs_threshold_ratio}}
+회신 ① {{due_initial}}   ②③ {{due_cause}}   ④ {{due_action}}   ⑤⑥ {{due_verify}}</t>
       </text>
     </comment>
     <comment ref="A12" authorId="0" shapeId="0">
       <text>
-        <t>시스템 자동 기입. 발행 검사 시각까지 동일 Job의 검사 완료 Unit 수 × 해당 부품 슬롯 수입니다. requested_quantity(목표 PASS 수량)가 아닙니다.</t>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0">
-      <text>
-        <t>시스템 자동 기입. 동일 Job·부품·불량 유형의 production.unit_defects 기록 수입니다. 불량 Unit 수와 다를 수 있습니다.</t>
-      </text>
-    </comment>
-    <comment ref="J12" authorId="0" shapeId="0">
-      <text>
-        <t>자동 계산. 관리자가 아래 검증 검사 수량·불량 수량을 입력하면 PPM을 계산합니다. 검사 시스템에서 재집계해 자동 채우는 값은 아닙니다.</t>
+        <t>실제 발주·입고 자료로 확인한 업체명. 데이터시트 공급사를 자동 전사하지 않습니다.</t>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <t>업체 담당자·직책·연락처. 접수 확인은 불량 근거에 기록합니다.</t>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0">
+      <text>
+        <t>요청 마감 일시와 시간대. 원인·대책 기한은 초동 조치 칸에 기록합니다.</t>
       </text>
     </comment>
     <comment ref="C13" authorId="0" shapeId="0">
@@ -1384,10 +1820,44 @@
         <t>시스템 자동 기입. 동일 Job 시작(없으면 요청) 시각부터 대상 검사 시각까지 누적 집계합니다. 기간 일수: {{window_days}}. 이동 7일 집계가 아닙니다.</t>
       </text>
     </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
-      <text>
-        <t>발행 시점 전체 슬롯 분포: {{hotspot}}
-전체 분포는 불량 근거 시트에 자동 기입됩니다.</t>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>동일 Job·부품·불량 유형, 대상 검사 시점까지 누적. 검사 수량은 검사 Unit 수 × 부품 슬롯 수. 폐기 수량이나 납품 Lot 불량률이 아닙니다.</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+자동 분석</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+관리자 직접 작성  |  ①~⑥ 조치·원인·대책·검증·종결</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+① 초동 조치</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+□ 생산 중단    □ 출하 보류    □ 재고 선별    □ 고객 통보    □ 설비 정지</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>당사 담당자가 작성: 조치 요청 범위 / 실제 실행 시각·확인자 / 확정·의심 수량 구분 / 초기·원인·대책 회신 마감 / 관련 문서번호. 자동 정지 완료로 해석하지 않습니다.</t>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+② 발생 원인</t>
       </text>
     </comment>
     <comment ref="C20" authorId="0" shapeId="0">
@@ -1395,9 +1865,73 @@
         <t>② 발생 원인의 핵심을 한 줄로 요약합니다.</t>
       </text>
     </comment>
+    <comment ref="C21" authorId="0" shapeId="0">
+      <text>
+        <t>거래처 또는 조치부서 회신: 발생 원인 + 재현·비교 시험 근거 + 책임 판단. 추정과 입증을 구분합니다.</t>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+③ 유출 원인</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0" shapeId="0">
+      <text>
+        <t>왜 기존 검사에서 발견하지 못했는지, 해당 검사 기준·검출 능력과 입증 자료를 적습니다.</t>
+      </text>
+    </comment>
+    <comment ref="A23" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+④ 재발방지
+대책</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>변경 내용, 담당자, 완료 예정·실제 일시, 적용 Lot 또는 Unit, 변경 승인·효과 검증 자료 번호.</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+⑤ 효과 검증</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+불량률(자동 계산)</t>
+      </text>
+    </comment>
     <comment ref="F26" authorId="0" shapeId="0">
       <text>
         <t>자동 계산. 검증 불량 수량 ÷ 검증 검사 수량. 검증 수량은 부품 검사 건수 기준입니다.</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+검증 수량: 부품 검사 건수 기준</t>
+      </text>
+    </comment>
+    <comment ref="A28" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+⑥ 종결</t>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+잔여 위험 · 이관 사항 확인</t>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+노랑: 관리자 작성 · 파랑: 자동 계산 · 그 외: 시스템 기입 / 입력 칸 클릭 시 작성 안내</t>
       </text>
     </comment>
   </commentList>
@@ -1410,9 +1944,34 @@
     <author>User</author>
   </authors>
   <commentList>
-    <comment ref="A9" authorId="0" shapeId="0">
-      <text>
-        <t>기존 생성기가 불량 기록별 Unit ID·검사 시각을 줄바꿈 목록으로 기입합니다. 슬롯 토큰은 중복 제거된 목록이며 개별 기록의 슬롯 열과 일대일 대응하지 않습니다. 운영 적용 전 목록 출력 경계의 정비가 필요합니다.</t>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>적용 규격·개정 / 허용 기준 / 실측값 / 시험·사진 번호</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>실제 납품업체 / PO·납품 번호 / 제조 Lot·Date Code / 입고일</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>확정 불량 / 의심 수량 / 재고·공정품·기출하 / 격리 위치</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>기판 기능 결과 / 재작업·폐기 판정 / 근거 번호</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>통보·접수 확인 일시 / 실제 회신 일시 / 관련 대책서 번호</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>정지·재개 확인자와 시각 / 공수·폐기 수량 / 비용 증빙</t>
       </text>
     </comment>
   </commentList>
@@ -1425,9 +1984,26 @@
     <author>User</author>
   </authors>
   <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+부품 검토자료 · 시스템 자동 기입</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>데이터시트의 공급사 정보입니다. 해당 불량품의 실제 납품업체·귀책과 연결되지 않습니다.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>이전 v2 내용(참고):
+Checklist 공통·부품별 항목을 함께 조회 · 원인·적합성 판단은 관리자 작성</t>
+      </text>
+    </comment>
     <comment ref="A18" authorId="0" shapeId="0">
       <text>
-        <t>현재 생성기는 후보별 행을 늘리지 않고 각 열에 줄바꿈 목록을 기입합니다. 후보 수가 늘거나 항목별 줄바꿈이 달라지면 행 단위 비교가 어려우므로 운영 적용 전 행 확장 검토가 필요합니다.</t>
+        <t>같은 부품 타입의 후보 목록이며 대체 승인 목록이 아닙니다. 원본 데이터시트에서 MPN별 정격·공급사·가격을 확인합니다.</t>
       </text>
     </comment>
   </commentList>
@@ -1440,10 +2016,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2857500"/>
+    <ext cx="2857500" cy="1609725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1468,10 +2044,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5905500" cy="2857500"/>
+    <ext cx="2857500" cy="1609725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1781,7 +2357,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00243D5B"/>
+    <tabColor rgb="00233D59"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -1803,7 +2379,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="91" t="inlineStr">
+      <c r="A1" s="161" t="inlineStr">
         <is>
           <t>불 량 대 책 서</t>
         </is>
@@ -1828,25 +2404,25 @@
       <c r="L1" s="123" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="G2" s="124" t="n"/>
-      <c r="H2" s="125" t="n"/>
-      <c r="I2" s="124" t="n"/>
-      <c r="J2" s="125" t="n"/>
-      <c r="K2" s="124" t="n"/>
-      <c r="L2" s="125" t="n"/>
+      <c r="G2" s="195" t="n"/>
+      <c r="H2" s="162" t="n"/>
+      <c r="I2" s="195" t="n"/>
+      <c r="J2" s="162" t="n"/>
+      <c r="K2" s="195" t="n"/>
+      <c r="L2" s="162" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="G3" s="126" t="n"/>
-      <c r="H3" s="127" t="n"/>
-      <c r="I3" s="126" t="n"/>
-      <c r="J3" s="127" t="n"/>
-      <c r="K3" s="126" t="n"/>
-      <c r="L3" s="127" t="n"/>
-    </row>
-    <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="128" t="inlineStr">
-        <is>
-          <t>시스템 자동 기입 · 발행 시점 고정  |  담당·기한·문서 상태는 관리자 갱신</t>
+      <c r="G3" s="163" t="n"/>
+      <c r="H3" s="164" t="n"/>
+      <c r="I3" s="163" t="n"/>
+      <c r="J3" s="164" t="n"/>
+      <c r="K3" s="163" t="n"/>
+      <c r="L3" s="164" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="199" t="inlineStr">
+        <is>
+          <t>01  발생 사실 · 시스템 자동 기입  |  확정 불량 개별 건 발행</t>
         </is>
       </c>
     </row>
@@ -1857,7 +2433,7 @@
         </is>
       </c>
       <c r="B5" s="123" t="n"/>
-      <c r="C5" s="129" t="inlineStr">
+      <c r="C5" s="200" t="inlineStr">
         <is>
           <t>{{alert_code}}</t>
         </is>
@@ -1872,7 +2448,7 @@
         </is>
       </c>
       <c r="I5" s="123" t="n"/>
-      <c r="J5" s="131" t="inlineStr">
+      <c r="J5" s="203" t="inlineStr">
         <is>
           <t>{{issued_at}}</t>
         </is>
@@ -1887,7 +2463,7 @@
         </is>
       </c>
       <c r="B6" s="123" t="n"/>
-      <c r="C6" s="129" t="inlineStr">
+      <c r="C6" s="200" t="inlineStr">
         <is>
           <t>{{part_id}} · {{part_name}} ({{category_label}})</t>
         </is>
@@ -1902,7 +2478,7 @@
         </is>
       </c>
       <c r="I6" s="123" t="n"/>
-      <c r="J6" s="131" t="inlineStr">
+      <c r="J6" s="203" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
@@ -1917,28 +2493,28 @@
         </is>
       </c>
       <c r="B7" s="123" t="n"/>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="204" t="inlineStr">
         <is>
           <t>{{assignee}}</t>
         </is>
       </c>
-      <c r="D7" s="133" t="n"/>
-      <c r="E7" s="133" t="n"/>
-      <c r="F7" s="133" t="n"/>
-      <c r="G7" s="134" t="n"/>
+      <c r="D7" s="166" t="n"/>
+      <c r="E7" s="166" t="n"/>
+      <c r="F7" s="166" t="n"/>
+      <c r="G7" s="167" t="n"/>
       <c r="H7" s="122" t="inlineStr">
         <is>
           <t>협조 부서</t>
         </is>
       </c>
       <c r="I7" s="123" t="n"/>
-      <c r="J7" s="135" t="inlineStr">
+      <c r="J7" s="207" t="inlineStr">
         <is>
           <t>{{support_teams}}</t>
         </is>
       </c>
-      <c r="K7" s="133" t="n"/>
-      <c r="L7" s="134" t="n"/>
+      <c r="K7" s="166" t="n"/>
+      <c r="L7" s="167" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="122" t="inlineStr">
@@ -1947,7 +2523,7 @@
         </is>
       </c>
       <c r="B8" s="123" t="n"/>
-      <c r="C8" s="136" t="inlineStr">
+      <c r="C8" s="208" t="inlineStr">
         <is>
           <t>Job {{job_id}}
 Unit {{target_unit_id}} · {{target_slot_code}}</t>
@@ -1963,7 +2539,7 @@
         </is>
       </c>
       <c r="I8" s="123" t="n"/>
-      <c r="J8" s="131" t="inlineStr">
+      <c r="J8" s="203" t="inlineStr">
         <is>
           <t>{{target_inspected_at}}</t>
         </is>
@@ -1971,84 +2547,64 @@
       <c r="K8" s="130" t="n"/>
       <c r="L8" s="123" t="n"/>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="137" t="inlineStr">
-        <is>
-          <t>상태 {{alert_status}} · 발행 기준 {{vs_threshold_ratio}}
-회신 ① {{due_initial}}   ②③ {{due_cause}}   ④ {{due_action}}   ⑤⑥ {{due_verify}}</t>
-        </is>
-      </c>
-      <c r="B9" s="133" t="n"/>
-      <c r="C9" s="133" t="n"/>
-      <c r="D9" s="133" t="n"/>
-      <c r="E9" s="133" t="n"/>
-      <c r="F9" s="133" t="n"/>
-      <c r="G9" s="133" t="n"/>
-      <c r="H9" s="133" t="n"/>
-      <c r="I9" s="133" t="n"/>
-      <c r="J9" s="133" t="n"/>
-      <c r="K9" s="133" t="n"/>
-      <c r="L9" s="134" t="n"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="169" t="inlineStr">
+        <is>
+          <t>문서 상태: 발행  |  확정 불량 1건 확인에 따른 통보 · 조치 실행 여부는 담당자 확인</t>
+        </is>
+      </c>
+      <c r="B9" s="166" t="n"/>
+      <c r="C9" s="166" t="n"/>
+      <c r="D9" s="166" t="n"/>
+      <c r="E9" s="166" t="n"/>
+      <c r="F9" s="166" t="n"/>
+      <c r="G9" s="166" t="n"/>
+      <c r="H9" s="166" t="n"/>
+      <c r="I9" s="166" t="n"/>
+      <c r="J9" s="166" t="n"/>
+      <c r="K9" s="166" t="n"/>
+      <c r="L9" s="167" t="n"/>
     </row>
     <row r="10" ht="6" customHeight="1"/>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="122" t="inlineStr">
-        <is>
-          <t>부품 검사 수량</t>
-        </is>
-      </c>
-      <c r="B11" s="130" t="n"/>
-      <c r="C11" s="123" t="n"/>
-      <c r="D11" s="122" t="inlineStr">
-        <is>
-          <t>불량 건수</t>
-        </is>
-      </c>
-      <c r="E11" s="130" t="n"/>
-      <c r="F11" s="123" t="n"/>
-      <c r="G11" s="122" t="inlineStr">
-        <is>
-          <t>발행 PPM</t>
-        </is>
-      </c>
-      <c r="H11" s="130" t="n"/>
-      <c r="I11" s="123" t="n"/>
-      <c r="J11" s="122" t="inlineStr">
-        <is>
-          <t>검증 PPM(계산)</t>
-        </is>
-      </c>
-      <c r="K11" s="130" t="n"/>
-      <c r="L11" s="123" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="138" t="inlineStr">
-        <is>
-          <t>{{inspected_quantity}}</t>
-        </is>
-      </c>
-      <c r="B12" s="130" t="n"/>
-      <c r="C12" s="123" t="n"/>
-      <c r="D12" s="138" t="inlineStr">
-        <is>
-          <t>{{defective_quantity}}</t>
-        </is>
-      </c>
-      <c r="E12" s="130" t="n"/>
-      <c r="F12" s="123" t="n"/>
-      <c r="G12" s="138" t="inlineStr">
-        <is>
-          <t>{{defect_ppm}}</t>
-        </is>
-      </c>
-      <c r="H12" s="130" t="n"/>
-      <c r="I12" s="123" t="n"/>
-      <c r="J12" s="139">
-        <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),I25/G25*1000000,"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="140" t="n"/>
-      <c r="L12" s="141" t="n"/>
+      <c r="A11" s="172" t="inlineStr">
+        <is>
+          <t>02  실제 납품업체 · 당사 작성</t>
+        </is>
+      </c>
+      <c r="B11" s="209" t="n"/>
+      <c r="C11" s="209" t="n"/>
+      <c r="D11" s="210" t="n"/>
+      <c r="E11" s="172" t="inlineStr">
+        <is>
+          <t>거래처 회신 책임자 · 당사 작성</t>
+        </is>
+      </c>
+      <c r="F11" s="209" t="n"/>
+      <c r="G11" s="209" t="n"/>
+      <c r="H11" s="210" t="n"/>
+      <c r="I11" s="172" t="inlineStr">
+        <is>
+          <t>초기 회신 기한 · 당사 작성</t>
+        </is>
+      </c>
+      <c r="J11" s="209" t="n"/>
+      <c r="K11" s="209" t="n"/>
+      <c r="L11" s="210" t="n"/>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="173" t="inlineStr"/>
+      <c r="B12" s="244" t="n"/>
+      <c r="C12" s="244" t="n"/>
+      <c r="D12" s="245" t="n"/>
+      <c r="E12" s="174" t="inlineStr"/>
+      <c r="F12" s="244" t="n"/>
+      <c r="G12" s="244" t="n"/>
+      <c r="H12" s="245" t="n"/>
+      <c r="I12" s="174" t="inlineStr"/>
+      <c r="J12" s="244" t="n"/>
+      <c r="K12" s="244" t="n"/>
+      <c r="L12" s="245" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="122" t="inlineStr">
@@ -2057,7 +2613,7 @@
         </is>
       </c>
       <c r="B13" s="123" t="n"/>
-      <c r="C13" s="142" t="inlineStr">
+      <c r="C13" s="213" t="inlineStr">
         <is>
           <t>{{period_start}}
 ~ {{period_end}} ({{evaluation_mode}})</t>
@@ -2073,7 +2629,7 @@
         </is>
       </c>
       <c r="I13" s="123" t="n"/>
-      <c r="J13" s="142" t="inlineStr">
+      <c r="J13" s="213" t="inlineStr">
         <is>
           <t>{{source_recipe_version}}</t>
         </is>
@@ -2082,44 +2638,31 @@
       <c r="L13" s="123" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="122" t="inlineStr">
-        <is>
-          <t>발생 위치</t>
-        </is>
-      </c>
-      <c r="B14" s="123" t="n"/>
-      <c r="C14" s="131" t="inlineStr">
-        <is>
-          <t>{{target_slot_code}} (발행 대상)
-전체 분포: 불량 근거</t>
-        </is>
-      </c>
-      <c r="D14" s="130" t="n"/>
-      <c r="E14" s="130" t="n"/>
-      <c r="F14" s="123" t="n"/>
-      <c r="G14" s="122" t="inlineStr">
-        <is>
-          <t>완제품 영향</t>
-        </is>
-      </c>
-      <c r="H14" s="123" t="n"/>
-      <c r="I14" s="131" t="inlineStr">
-        <is>
-          <t>{{unit_impact}}</t>
-        </is>
-      </c>
-      <c r="J14" s="130" t="n"/>
-      <c r="K14" s="130" t="n"/>
-      <c r="L14" s="123" t="n"/>
+      <c r="A14" s="214" t="inlineStr">
+        <is>
+          <t>누적 참고 | 부품 검사 {{inspected_quantity}}건 · 불량 {{defective_quantity}}건 · {{defect_ppm}} PPM · 불량 Unit {{unit_impact}}</t>
+        </is>
+      </c>
+      <c r="B14" s="209" t="n"/>
+      <c r="C14" s="209" t="n"/>
+      <c r="D14" s="209" t="n"/>
+      <c r="E14" s="209" t="n"/>
+      <c r="F14" s="209" t="n"/>
+      <c r="G14" s="209" t="n"/>
+      <c r="H14" s="209" t="n"/>
+      <c r="I14" s="209" t="n"/>
+      <c r="J14" s="209" t="n"/>
+      <c r="K14" s="209" t="n"/>
+      <c r="L14" s="210" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="122" t="inlineStr">
         <is>
-          <t>자동 분석</t>
+          <t>확인 사실</t>
         </is>
       </c>
       <c r="B15" s="123" t="n"/>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="203" t="inlineStr">
         <is>
           <t>{{auto_analysis}}</t>
         </is>
@@ -2136,9 +2679,9 @@
     </row>
     <row r="16" ht="6" customHeight="1"/>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="143" t="inlineStr">
-        <is>
-          <t>관리자 직접 작성  |  ①~⑥ 조치·원인·대책·검증·종결</t>
+      <c r="A17" s="217" t="inlineStr">
+        <is>
+          <t>03  조치 및 회신  |  당사 작성 → 거래처·조치부서 회신 → 당사 검증</t>
         </is>
       </c>
       <c r="B17" s="130" t="n"/>
@@ -2156,112 +2699,116 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="122" t="inlineStr">
         <is>
-          <t>① 초동 조치</t>
+          <t>① 당사
+초동·요청</t>
         </is>
       </c>
       <c r="B18" s="144" t="n"/>
-      <c r="C18" s="145" t="inlineStr">
-        <is>
-          <t>□ 생산 중단    □ 출하 보류    □ 재고 선별    □ 고객 통보    □ 설비 정지</t>
-        </is>
-      </c>
-      <c r="D18" s="133" t="n"/>
-      <c r="E18" s="133" t="n"/>
-      <c r="F18" s="133" t="n"/>
-      <c r="G18" s="133" t="n"/>
-      <c r="H18" s="133" t="n"/>
-      <c r="I18" s="133" t="n"/>
-      <c r="J18" s="133" t="n"/>
-      <c r="K18" s="133" t="n"/>
-      <c r="L18" s="134" t="n"/>
+      <c r="C18" s="218" t="inlineStr">
+        <is>
+          <t>요청  □ 생산 보류  □ 출하 보류  □ 격리·선별  □ 원인 분석  □ 기존 대책 연계</t>
+        </is>
+      </c>
+      <c r="D18" s="166" t="n"/>
+      <c r="E18" s="166" t="n"/>
+      <c r="F18" s="166" t="n"/>
+      <c r="G18" s="166" t="n"/>
+      <c r="H18" s="166" t="n"/>
+      <c r="I18" s="166" t="n"/>
+      <c r="J18" s="166" t="n"/>
+      <c r="K18" s="166" t="n"/>
+      <c r="L18" s="167" t="n"/>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="146" t="n"/>
       <c r="B19" s="147" t="n"/>
-      <c r="C19" s="132" t="n"/>
-      <c r="D19" s="133" t="n"/>
-      <c r="E19" s="133" t="n"/>
-      <c r="F19" s="133" t="n"/>
-      <c r="G19" s="133" t="n"/>
-      <c r="H19" s="133" t="n"/>
-      <c r="I19" s="133" t="n"/>
-      <c r="J19" s="133" t="n"/>
-      <c r="K19" s="133" t="n"/>
-      <c r="L19" s="134" t="n"/>
+      <c r="C19" s="204" t="inlineStr"/>
+      <c r="D19" s="166" t="n"/>
+      <c r="E19" s="166" t="n"/>
+      <c r="F19" s="166" t="n"/>
+      <c r="G19" s="166" t="n"/>
+      <c r="H19" s="166" t="n"/>
+      <c r="I19" s="166" t="n"/>
+      <c r="J19" s="166" t="n"/>
+      <c r="K19" s="166" t="n"/>
+      <c r="L19" s="167" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="122" t="inlineStr">
         <is>
-          <t>② 발생 원인</t>
+          <t>② 회신
+발생 원인</t>
         </is>
       </c>
       <c r="B20" s="144" t="n"/>
-      <c r="C20" s="148" t="n"/>
-      <c r="D20" s="133" t="n"/>
-      <c r="E20" s="133" t="n"/>
-      <c r="F20" s="133" t="n"/>
-      <c r="G20" s="133" t="n"/>
-      <c r="H20" s="133" t="n"/>
-      <c r="I20" s="133" t="n"/>
-      <c r="J20" s="133" t="n"/>
-      <c r="K20" s="133" t="n"/>
-      <c r="L20" s="134" t="n"/>
-    </row>
-    <row r="21" ht="56" customHeight="1">
+      <c r="C20" s="219" t="inlineStr"/>
+      <c r="D20" s="166" t="n"/>
+      <c r="E20" s="166" t="n"/>
+      <c r="F20" s="166" t="n"/>
+      <c r="G20" s="166" t="n"/>
+      <c r="H20" s="166" t="n"/>
+      <c r="I20" s="166" t="n"/>
+      <c r="J20" s="166" t="n"/>
+      <c r="K20" s="166" t="n"/>
+      <c r="L20" s="167" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
       <c r="A21" s="146" t="n"/>
       <c r="B21" s="147" t="n"/>
-      <c r="C21" s="132" t="n"/>
-      <c r="D21" s="133" t="n"/>
-      <c r="E21" s="133" t="n"/>
-      <c r="F21" s="133" t="n"/>
-      <c r="G21" s="133" t="n"/>
-      <c r="H21" s="133" t="n"/>
-      <c r="I21" s="133" t="n"/>
-      <c r="J21" s="133" t="n"/>
-      <c r="K21" s="133" t="n"/>
-      <c r="L21" s="134" t="n"/>
-    </row>
-    <row r="22" ht="53" customHeight="1">
+      <c r="C21" s="219" t="inlineStr"/>
+      <c r="D21" s="166" t="n"/>
+      <c r="E21" s="166" t="n"/>
+      <c r="F21" s="166" t="n"/>
+      <c r="G21" s="166" t="n"/>
+      <c r="H21" s="166" t="n"/>
+      <c r="I21" s="166" t="n"/>
+      <c r="J21" s="166" t="n"/>
+      <c r="K21" s="166" t="n"/>
+      <c r="L21" s="167" t="n"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
       <c r="A22" s="122" t="inlineStr">
         <is>
-          <t>③ 유출 원인</t>
+          <t>③ 회신
+유출 원인</t>
         </is>
       </c>
       <c r="B22" s="123" t="n"/>
-      <c r="C22" s="132" t="n"/>
-      <c r="D22" s="133" t="n"/>
-      <c r="E22" s="133" t="n"/>
-      <c r="F22" s="133" t="n"/>
-      <c r="G22" s="133" t="n"/>
-      <c r="H22" s="133" t="n"/>
-      <c r="I22" s="133" t="n"/>
-      <c r="J22" s="133" t="n"/>
-      <c r="K22" s="133" t="n"/>
-      <c r="L22" s="134" t="n"/>
-    </row>
-    <row r="23" ht="55" customHeight="1">
+      <c r="C22" s="219" t="inlineStr"/>
+      <c r="D22" s="166" t="n"/>
+      <c r="E22" s="166" t="n"/>
+      <c r="F22" s="166" t="n"/>
+      <c r="G22" s="166" t="n"/>
+      <c r="H22" s="166" t="n"/>
+      <c r="I22" s="166" t="n"/>
+      <c r="J22" s="166" t="n"/>
+      <c r="K22" s="166" t="n"/>
+      <c r="L22" s="167" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="122" t="inlineStr">
         <is>
-          <t>④ 재발방지
-대책</t>
+          <t>④ 회신
+영구 대책</t>
         </is>
       </c>
       <c r="B23" s="123" t="n"/>
-      <c r="C23" s="132" t="n"/>
-      <c r="D23" s="133" t="n"/>
-      <c r="E23" s="133" t="n"/>
-      <c r="F23" s="133" t="n"/>
-      <c r="G23" s="133" t="n"/>
-      <c r="H23" s="133" t="n"/>
-      <c r="I23" s="133" t="n"/>
-      <c r="J23" s="133" t="n"/>
-      <c r="K23" s="133" t="n"/>
-      <c r="L23" s="134" t="n"/>
+      <c r="C23" s="219" t="inlineStr"/>
+      <c r="D23" s="166" t="n"/>
+      <c r="E23" s="166" t="n"/>
+      <c r="F23" s="166" t="n"/>
+      <c r="G23" s="166" t="n"/>
+      <c r="H23" s="166" t="n"/>
+      <c r="I23" s="166" t="n"/>
+      <c r="J23" s="166" t="n"/>
+      <c r="K23" s="166" t="n"/>
+      <c r="L23" s="167" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="122" t="inlineStr">
         <is>
-          <t>⑤ 효과 검증</t>
+          <t>⑤ 당사
+효과 검증</t>
         </is>
       </c>
       <c r="B24" s="144" t="n"/>
@@ -2299,40 +2846,39 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="149" t="n"/>
       <c r="B25" s="150" t="n"/>
-      <c r="C25" s="151" t="n"/>
-      <c r="D25" s="134" t="n"/>
-      <c r="E25" s="151" t="n"/>
-      <c r="F25" s="134" t="n"/>
-      <c r="G25" s="152" t="n"/>
-      <c r="H25" s="134" t="n"/>
-      <c r="I25" s="152" t="n"/>
-      <c r="J25" s="134" t="n"/>
-      <c r="K25" s="151" t="inlineStr">
+      <c r="C25" s="220" t="n"/>
+      <c r="D25" s="167" t="n"/>
+      <c r="E25" s="220" t="n"/>
+      <c r="F25" s="167" t="n"/>
+      <c r="G25" s="221" t="n"/>
+      <c r="H25" s="167" t="n"/>
+      <c r="I25" s="221" t="n"/>
+      <c r="J25" s="167" t="n"/>
+      <c r="K25" s="220" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="L25" s="134" t="n"/>
+      <c r="L25" s="167" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="149" t="n"/>
       <c r="B26" s="150" t="n"/>
       <c r="C26" s="122" t="inlineStr">
         <is>
-          <t>불량률(자동 계산)</t>
+          <t>불량률 · 자동 계산</t>
         </is>
       </c>
       <c r="D26" s="130" t="n"/>
       <c r="E26" s="123" t="n"/>
-      <c r="F26" s="153">
+      <c r="F26" s="222">
         <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),I25/G25,"")</f>
         <v/>
       </c>
-      <c r="G26" s="141" t="n"/>
-      <c r="H26" s="136" t="inlineStr">
-        <is>
-          <t>검증 수량: 부품 검사 건수 기준</t>
-        </is>
+      <c r="G26" s="123" t="n"/>
+      <c r="H26" s="223">
+        <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),"검증 PPM  "&amp;TEXT(I25/G25*1000000,"#,##0"),"검증 PPM  —")</f>
+        <v/>
       </c>
       <c r="I26" s="130" t="n"/>
       <c r="J26" s="130" t="n"/>
@@ -2342,21 +2888,22 @@
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="146" t="n"/>
       <c r="B27" s="147" t="n"/>
-      <c r="C27" s="132" t="n"/>
-      <c r="D27" s="133" t="n"/>
-      <c r="E27" s="133" t="n"/>
-      <c r="F27" s="133" t="n"/>
-      <c r="G27" s="133" t="n"/>
-      <c r="H27" s="133" t="n"/>
-      <c r="I27" s="133" t="n"/>
-      <c r="J27" s="133" t="n"/>
-      <c r="K27" s="133" t="n"/>
-      <c r="L27" s="134" t="n"/>
+      <c r="C27" s="204" t="inlineStr"/>
+      <c r="D27" s="166" t="n"/>
+      <c r="E27" s="166" t="n"/>
+      <c r="F27" s="166" t="n"/>
+      <c r="G27" s="166" t="n"/>
+      <c r="H27" s="166" t="n"/>
+      <c r="I27" s="166" t="n"/>
+      <c r="J27" s="166" t="n"/>
+      <c r="K27" s="166" t="n"/>
+      <c r="L27" s="167" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="122" t="inlineStr">
         <is>
-          <t>⑥ 종결</t>
+          <t>⑥ 당사
+승인·종결</t>
         </is>
       </c>
       <c r="B28" s="144" t="n"/>
@@ -2366,12 +2913,12 @@
         </is>
       </c>
       <c r="D28" s="123" t="n"/>
-      <c r="E28" s="132" t="n"/>
-      <c r="F28" s="133" t="n"/>
-      <c r="G28" s="134" t="n"/>
+      <c r="E28" s="204" t="n"/>
+      <c r="F28" s="166" t="n"/>
+      <c r="G28" s="167" t="n"/>
       <c r="H28" s="154" t="inlineStr">
         <is>
-          <t>잔여 위험 · 이관 사항 확인</t>
+          <t>재개·출하 승인 및 잔여 사항</t>
         </is>
       </c>
       <c r="I28" s="130" t="n"/>
@@ -2382,102 +2929,97 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="146" t="n"/>
       <c r="B29" s="147" t="n"/>
-      <c r="C29" s="132" t="n"/>
-      <c r="D29" s="133" t="n"/>
-      <c r="E29" s="133" t="n"/>
-      <c r="F29" s="133" t="n"/>
-      <c r="G29" s="133" t="n"/>
-      <c r="H29" s="133" t="n"/>
-      <c r="I29" s="133" t="n"/>
-      <c r="J29" s="133" t="n"/>
-      <c r="K29" s="133" t="n"/>
-      <c r="L29" s="134" t="n"/>
+      <c r="C29" s="204" t="inlineStr"/>
+      <c r="D29" s="166" t="n"/>
+      <c r="E29" s="166" t="n"/>
+      <c r="F29" s="166" t="n"/>
+      <c r="G29" s="166" t="n"/>
+      <c r="H29" s="166" t="n"/>
+      <c r="I29" s="166" t="n"/>
+      <c r="J29" s="166" t="n"/>
+      <c r="K29" s="166" t="n"/>
+      <c r="L29" s="167" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="155" t="inlineStr">
-        <is>
-          <t>노랑: 관리자 작성 · 파랑: 자동 계산 · 그 외: 시스템 기입 / 입력 칸 클릭 시 작성 안내</t>
+      <c r="A30" s="185" t="inlineStr">
+        <is>
+          <t>연녹색: 자동 기입·자동 계산  |  연노랑: 수동 작성(당사·거래처)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="75">
+  <mergeCells count="70">
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="J6:L6"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="E28:G28"/>
     <mergeCell ref="K25:L25"/>
+    <mergeCell ref="H26:L26"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C6:G6"/>
+    <mergeCell ref="K24:L24"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="H26:L26"/>
     <mergeCell ref="K2:L3"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="A18:B19"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="J7:L7"/>
     <mergeCell ref="C19:L19"/>
-    <mergeCell ref="E28:G28"/>
     <mergeCell ref="A20:B21"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E12:H12"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="A14:L14"/>
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="A17:L17"/>
-    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="F26:G26"/>
-    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="I11:L11"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A28:B29"/>
     <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A24:B27"/>
+    <mergeCell ref="G2:H3"/>
+    <mergeCell ref="I24:J24"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="G2:H3"/>
-    <mergeCell ref="A24:B27"/>
-    <mergeCell ref="I24:J24"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="J8:L8"/>
+    <mergeCell ref="C20:L20"/>
     <mergeCell ref="H28:L28"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:H14"/>
     <mergeCell ref="A9:L9"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="C20:L20"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="H13:I13"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G11:I11"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="A1:F3"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="C26:E26"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="H5:I5"/>
     <mergeCell ref="C21:L21"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C28:D28"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="E11:H11"/>
   </mergeCells>
   <conditionalFormatting sqref="K25:L25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
@@ -2490,7 +3032,7 @@
       <formula>"PENDING"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="18">
+  <dataValidations count="19">
     <dataValidation sqref="J6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="참고 시트 2개은 유형과 무관하게 항상 첨부한다.&#10;어느 자료가 이번 건에 쓸모 있는지는 담당자가 판단한다." type="list">
       <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
     </dataValidation>
@@ -2517,6 +3059,9 @@
     <dataValidation sqref="C27" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;"/>
     <dataValidation sqref="E28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt=""/>
     <dataValidation sqref="C29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;"/>
+    <dataValidation sqref="G25 I25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.32" right="0.32" top="0.32" bottom="0.32" header="0.1" footer="0.1"/>
@@ -2528,228 +3073,324 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00627083"/>
+    <tabColor rgb="00233D59"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="156" t="inlineStr">
-        <is>
-          <t>불량 근거 · 시스템 자동 기입 / 발행 시점 고정</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="70" t="inlineStr">
-        <is>
-          <t>production.unit_defects 확정 기록 · 문서번호 {{alert_code}} · 수정 금지</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="71" t="inlineStr">
-        <is>
-          <t>슬롯별 발생 분포        어느 슬롯에 몰려 있는지 · 공정 원인 판단의 1차 근거</t>
-        </is>
-      </c>
-      <c r="B3" s="36" t="n"/>
-      <c r="C3" s="36" t="n"/>
-      <c r="D3" s="36" t="n"/>
-      <c r="E3" s="30" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="72" t="inlineStr">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="186" t="inlineStr">
+        <is>
+          <t>불량 근거 및 납품 추적</t>
+        </is>
+      </c>
+      <c r="B1" s="246" t="n"/>
+      <c r="C1" s="246" t="n"/>
+      <c r="D1" s="246" t="n"/>
+      <c r="E1" s="247" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="187" t="inlineStr">
+        <is>
+          <t>연녹색: 시스템 자동 기입 · 연노랑: 담당자 수동 작성</t>
+        </is>
+      </c>
+      <c r="B2" s="246" t="n"/>
+      <c r="C2" s="246" t="n"/>
+      <c r="D2" s="246" t="n"/>
+      <c r="E2" s="247" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="190" t="inlineStr">
+        <is>
+          <t>01  발행 대상 · 시스템 자동 기입</t>
+        </is>
+      </c>
+      <c r="B3" s="248" t="n"/>
+      <c r="C3" s="248" t="n"/>
+      <c r="D3" s="248" t="n"/>
+      <c r="E3" s="249" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="224" t="inlineStr">
+        <is>
+          <t>문서 {{alert_code}} · 불량 ID {{unit_defect_id}} · Unit {{target_unit_id}}</t>
+        </is>
+      </c>
+      <c r="B4" s="215" t="n"/>
+      <c r="C4" s="215" t="n"/>
+      <c r="D4" s="215" t="n"/>
+      <c r="E4" s="216" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="224" t="inlineStr">
+        <is>
+          <t>슬롯 {{target_slot_code}} · {{defect_type}} · 검사 {{target_inspected_at}}</t>
+        </is>
+      </c>
+      <c r="B5" s="215" t="n"/>
+      <c r="C5" s="215" t="n"/>
+      <c r="D5" s="215" t="n"/>
+      <c r="E5" s="216" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="190" t="inlineStr">
+        <is>
+          <t>02  동일 Job·부품·유형 누적 · 발행 시점 참고</t>
+        </is>
+      </c>
+      <c r="B6" s="248" t="n"/>
+      <c r="C6" s="248" t="n"/>
+      <c r="D6" s="248" t="n"/>
+      <c r="E6" s="249" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="172" t="inlineStr">
         <is>
           <t>슬롯</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B7" s="172" t="inlineStr">
         <is>
           <t>불량 건수</t>
         </is>
       </c>
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C7" s="172" t="inlineStr">
         <is>
           <t>슬롯 불량률</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="E4" s="30" t="n"/>
-    </row>
-    <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="73" t="inlineStr">
+      <c r="D7" s="172" t="inlineStr">
+        <is>
+          <t>집계 기준</t>
+        </is>
+      </c>
+      <c r="E7" s="172" t="inlineStr">
+        <is>
+          <t>해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="214" t="inlineStr">
         <is>
           <t>{{slot_code}}</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B8" s="214" t="inlineStr">
         <is>
           <t>{{count}}</t>
         </is>
       </c>
-      <c r="C5" s="75" t="inlineStr">
+      <c r="C8" s="214" t="inlineStr">
         <is>
           <t>{{slot_rate}}</t>
         </is>
       </c>
-      <c r="D5" s="76" t="inlineStr">
+      <c r="D8" s="214" t="inlineStr">
         <is>
           <t>{{slot_note}}</t>
         </is>
       </c>
-      <c r="E5" s="30" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1"/>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="71" t="inlineStr">
-        <is>
-          <t>불량 유닛 목록</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="30" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="72" t="inlineStr">
-        <is>
-          <t>unit_id</t>
-        </is>
-      </c>
-      <c r="B8" s="72" t="inlineStr">
-        <is>
-          <t>슬롯</t>
-        </is>
-      </c>
-      <c r="C8" s="72" t="inlineStr">
-        <is>
-          <t>불량 유형</t>
-        </is>
-      </c>
-      <c r="D8" s="72" t="inlineStr">
-        <is>
-          <t>검사 시각</t>
-        </is>
-      </c>
-      <c r="E8" s="72" t="inlineStr">
-        <is>
-          <t>검사 이미지 경로</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="73" t="inlineStr">
-        <is>
-          <t>{{unit_id}}</t>
-        </is>
-      </c>
-      <c r="B9" s="73" t="inlineStr">
-        <is>
-          <t>{{slot_code}}</t>
-        </is>
-      </c>
-      <c r="C9" s="73" t="inlineStr">
-        <is>
-          <t>{{defect_type}}</t>
-        </is>
-      </c>
-      <c r="D9" s="73" t="inlineStr">
-        <is>
-          <t>{{inspected_at}}</t>
-        </is>
-      </c>
-      <c r="E9" s="76" t="inlineStr">
-        <is>
-          <t>{{inspection_image_path}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1"/>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="71" t="inlineStr">
-        <is>
-          <t>검사 이미지</t>
-        </is>
-      </c>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="36" t="n"/>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="30" t="n"/>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="77" t="inlineStr">
-        <is>
-          <t>{{inspection_image_status}} · {{inspection_image_path}} · SHA-256 {{inspection_image_sha256}}</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="36" t="n"/>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="30" t="n"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="34" t="n"/>
-      <c r="B13" s="78" t="n"/>
-      <c r="C13" s="78" t="n"/>
-      <c r="D13" s="78" t="n"/>
-      <c r="E13" s="79" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="80" t="n"/>
-      <c r="E14" s="81" t="n"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="80" t="n"/>
-      <c r="E15" s="81" t="n"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="80" t="n"/>
-      <c r="E16" s="81" t="n"/>
+      <c r="E8" s="187" t="inlineStr">
+        <is>
+          <t>전체 폐기·공급사 귀책을 뜻하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="190" t="inlineStr">
+        <is>
+          <t>03  판정·납품 추적 · 당사 담당자 작성</t>
+        </is>
+      </c>
+      <c r="B9" s="248" t="n"/>
+      <c r="C9" s="248" t="n"/>
+      <c r="D9" s="248" t="n"/>
+      <c r="E9" s="249" t="n"/>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="190" t="inlineStr">
+        <is>
+          <t>판정 근거</t>
+        </is>
+      </c>
+      <c r="B10" s="174" t="inlineStr"/>
+      <c r="C10" s="211" t="n"/>
+      <c r="D10" s="211" t="n"/>
+      <c r="E10" s="212" t="n"/>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="190" t="inlineStr">
+        <is>
+          <t>납품 추적</t>
+        </is>
+      </c>
+      <c r="B11" s="174" t="inlineStr"/>
+      <c r="C11" s="211" t="n"/>
+      <c r="D11" s="211" t="n"/>
+      <c r="E11" s="212" t="n"/>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="190" t="inlineStr">
+        <is>
+          <t>영향·격리</t>
+        </is>
+      </c>
+      <c r="B12" s="174" t="inlineStr"/>
+      <c r="C12" s="211" t="n"/>
+      <c r="D12" s="211" t="n"/>
+      <c r="E12" s="212" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="190" t="inlineStr">
+        <is>
+          <t>기능·처분</t>
+        </is>
+      </c>
+      <c r="B13" s="174" t="inlineStr"/>
+      <c r="C13" s="211" t="n"/>
+      <c r="D13" s="211" t="n"/>
+      <c r="E13" s="212" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="190" t="inlineStr">
+        <is>
+          <t>접수·회신</t>
+        </is>
+      </c>
+      <c r="B14" s="174" t="inlineStr"/>
+      <c r="C14" s="211" t="n"/>
+      <c r="D14" s="211" t="n"/>
+      <c r="E14" s="212" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="190" t="inlineStr">
+        <is>
+          <t>정지·손실</t>
+        </is>
+      </c>
+      <c r="B15" s="174" t="inlineStr"/>
+      <c r="C15" s="211" t="n"/>
+      <c r="D15" s="211" t="n"/>
+      <c r="E15" s="212" t="n"/>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="190" t="inlineStr">
+        <is>
+          <t>04  검사 이미지 · 시스템 첨부</t>
+        </is>
+      </c>
+      <c r="B16" s="248" t="n"/>
+      <c r="C16" s="248" t="n"/>
+      <c r="D16" s="248" t="n"/>
+      <c r="E16" s="249" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="80" t="n"/>
-      <c r="E17" s="81" t="n"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="82" t="n"/>
-      <c r="B18" s="83" t="n"/>
-      <c r="C18" s="83" t="n"/>
-      <c r="D18" s="83" t="n"/>
-      <c r="E18" s="84" t="n"/>
+      <c r="A17" s="225" t="inlineStr">
+        <is>
+          <t>{{inspection_image_status}} · {{inspection_image_path}}
+SHA-256 {{inspection_image_sha256}}</t>
+        </is>
+      </c>
+      <c r="B17" s="215" t="n"/>
+      <c r="C17" s="215" t="n"/>
+      <c r="D17" s="215" t="n"/>
+      <c r="E17" s="216" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="224" t="inlineStr"/>
+      <c r="B18" s="226" t="n"/>
+      <c r="C18" s="226" t="n"/>
+      <c r="D18" s="226" t="n"/>
+      <c r="E18" s="227" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="228" t="n"/>
+      <c r="B19" s="229" t="n"/>
+      <c r="C19" s="229" t="n"/>
+      <c r="D19" s="229" t="n"/>
+      <c r="E19" s="230" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="228" t="n"/>
+      <c r="B20" s="229" t="n"/>
+      <c r="C20" s="229" t="n"/>
+      <c r="D20" s="229" t="n"/>
+      <c r="E20" s="230" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="228" t="n"/>
+      <c r="B21" s="229" t="n"/>
+      <c r="C21" s="229" t="n"/>
+      <c r="D21" s="229" t="n"/>
+      <c r="E21" s="230" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="228" t="n"/>
+      <c r="B22" s="229" t="n"/>
+      <c r="C22" s="229" t="n"/>
+      <c r="D22" s="229" t="n"/>
+      <c r="E22" s="230" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="231" t="n"/>
+      <c r="B23" s="232" t="n"/>
+      <c r="C23" s="232" t="n"/>
+      <c r="D23" s="232" t="n"/>
+      <c r="E23" s="233" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
-  <mergeCells count="9">
-    <mergeCell ref="A12:E12"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="32">
+    <mergeCell ref="A8"/>
+    <mergeCell ref="C8"/>
+    <mergeCell ref="C7"/>
+    <mergeCell ref="D8"/>
+    <mergeCell ref="E7"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A13"/>
+    <mergeCell ref="A18:E23"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15"/>
+    <mergeCell ref="B7"/>
+    <mergeCell ref="A11"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="E8"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A13:E18"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B8"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="D7"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A14"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.32" right="0.32" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 불량 근거&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 불량 근거&amp;C&amp;8 연녹색: 자동 | 연노랑: 수동&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2763,7 +3404,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="008296AD"/>
+    <tabColor rgb="008797A7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -2779,85 +3420,95 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="157" t="inlineStr">
-        <is>
-          <t>부품 검토자료 · 시스템 자동 기입</t>
+      <c r="A1" s="192" t="inlineStr">
+        <is>
+          <t>부품 검토자료 · 내부 참고</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="86" t="inlineStr">
+      <c r="A2" s="234" t="inlineStr">
         <is>
           <t>부품 범주 {{category_label}} · 데이터시트 대조 {{datasheet_match}} · 기준일 {{source_dated_on}} · 조회 {{queried_at}}</t>
         </is>
       </c>
+      <c r="B2" s="229" t="n"/>
+      <c r="C2" s="229" t="n"/>
+      <c r="D2" s="229" t="n"/>
+      <c r="E2" s="229" t="n"/>
+      <c r="F2" s="229" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="250" t="inlineStr">
         <is>
           <t>현재 부품  |  데이터시트 대조</t>
         </is>
       </c>
+      <c r="B3" s="251" t="n"/>
+      <c r="C3" s="251" t="n"/>
+      <c r="D3" s="251" t="n"/>
+      <c r="E3" s="251" t="n"/>
+      <c r="F3" s="251" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="235" t="inlineStr">
         <is>
           <t>현재 MPN</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="235" t="inlineStr">
         <is>
           <t>핵심 정격</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
-        <is>
-          <t>공급사</t>
-        </is>
-      </c>
-      <c r="D4" s="158" t="inlineStr">
+      <c r="C4" s="235" t="inlineStr">
+        <is>
+          <t>자료상 공급사</t>
+        </is>
+      </c>
+      <c r="D4" s="236" t="inlineStr">
         <is>
           <t>단가(USD)</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="235" t="inlineStr">
         <is>
           <t>가격 기준 수량</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="235" t="inlineStr">
         <is>
           <t>가격 확인일</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="237" t="inlineStr">
         <is>
           <t>{{selected_mpn}}</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
+      <c r="B5" s="237" t="inlineStr">
         <is>
           <t>{{selected_spec}}</t>
         </is>
       </c>
-      <c r="C5" s="50" t="inlineStr">
+      <c r="C5" s="237" t="inlineStr">
         <is>
           <t>{{selected_supplier}}</t>
         </is>
       </c>
-      <c r="D5" s="57" t="inlineStr">
+      <c r="D5" s="238" t="inlineStr">
         <is>
           <t>{{selected_unit_price}}</t>
         </is>
       </c>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="E5" s="239" t="inlineStr">
         <is>
           <t>{{selected_price_basis}}</t>
         </is>
       </c>
-      <c r="F5" s="57" t="inlineStr">
+      <c r="F5" s="239" t="inlineStr">
         <is>
           <t>{{selected_price_checked_at}}</t>
         </is>
@@ -2872,74 +3523,93 @@
       <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="53" t="inlineStr">
+      <c r="A7" s="250" t="inlineStr">
         <is>
           <t>품질 체크리스트  |  공통 기준 + 부품별 기준</t>
         </is>
       </c>
+      <c r="B7" s="251" t="n"/>
+      <c r="C7" s="251" t="n"/>
+      <c r="D7" s="251" t="n"/>
+      <c r="E7" s="251" t="n"/>
+      <c r="F7" s="251" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="235" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="235" t="inlineStr">
         <is>
           <t>확인 항목</t>
         </is>
       </c>
-      <c r="E8" s="49" t="inlineStr">
+      <c r="C8" s="251" t="n"/>
+      <c r="D8" s="251" t="n"/>
+      <c r="E8" s="235" t="inlineStr">
         <is>
           <t>이상 시 조치</t>
         </is>
       </c>
+      <c r="F8" s="251" t="n"/>
     </row>
     <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="235" t="inlineStr">
         <is>
           <t>입고 검사</t>
         </is>
       </c>
-      <c r="B9" s="159" t="inlineStr">
+      <c r="B9" s="240" t="inlineStr">
         <is>
           <t>{{incoming_inspection}}</t>
         </is>
       </c>
-      <c r="E9" s="159" t="inlineStr">
+      <c r="C9" s="229" t="n"/>
+      <c r="D9" s="229" t="n"/>
+      <c r="E9" s="240" t="inlineStr">
         <is>
           <t>{{action_on_anomaly}}</t>
         </is>
       </c>
+      <c r="F9" s="229" t="n"/>
     </row>
     <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="235" t="inlineStr">
         <is>
           <t>조립·보관</t>
         </is>
       </c>
-      <c r="B10" s="159" t="inlineStr">
+      <c r="B10" s="240" t="inlineStr">
         <is>
           <t>{{assembly_control}}</t>
         </is>
       </c>
+      <c r="C10" s="229" t="n"/>
+      <c r="D10" s="229" t="n"/>
+      <c r="E10" s="229" t="n"/>
+      <c r="F10" s="229" t="n"/>
     </row>
     <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="235" t="inlineStr">
         <is>
           <t>기능·신뢰성</t>
         </is>
       </c>
-      <c r="B11" s="159" t="inlineStr">
+      <c r="B11" s="240" t="inlineStr">
         <is>
           <t>{{reliability_test}}</t>
         </is>
       </c>
+      <c r="C11" s="229" t="n"/>
+      <c r="D11" s="229" t="n"/>
+      <c r="E11" s="229" t="n"/>
+      <c r="F11" s="229" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t>Checklist 공통·부품별 항목을 함께 조회 · 원인·적합성 판단은 관리자 작성</t>
+      <c r="A12" s="193" t="inlineStr">
+        <is>
+          <t>연녹색: 데이터시트 자동 조회 · 수동 입력란 없음 · 실제 조치 결과는 담당자 확인</t>
         </is>
       </c>
     </row>
@@ -2952,91 +3622,73 @@
       <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="250" t="inlineStr">
         <is>
           <t>대체품 후보  |  적합성 검증·변경 승인 후 적용</t>
         </is>
       </c>
+      <c r="B14" s="251" t="n"/>
+      <c r="C14" s="251" t="n"/>
+      <c r="D14" s="251" t="n"/>
+      <c r="E14" s="251" t="n"/>
+      <c r="F14" s="251" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="87" t="inlineStr">
+      <c r="A15" s="241" t="inlineStr">
         <is>
           <t>같은 부품 타입이라는 것 외에 검증된 것은 없다 · 동일 정격만으로 drop-in 판단 금지 · 핀/패키지/정격/열/수명 재검증과 변경 승인을 거친 뒤에만 적용한다.</t>
         </is>
       </c>
+      <c r="B15" s="251" t="n"/>
+      <c r="C15" s="251" t="n"/>
+      <c r="D15" s="251" t="n"/>
+      <c r="E15" s="251" t="n"/>
+      <c r="F15" s="251" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="234" t="inlineStr">
         <is>
           <t>같은 타입 후보 {{candidate_count}}종 · 단가 {{price_range}} · 현재 선정 {{price_selected}} · 호환성 미승인</t>
         </is>
       </c>
+      <c r="B16" s="229" t="n"/>
+      <c r="C16" s="229" t="n"/>
+      <c r="D16" s="229" t="n"/>
+      <c r="E16" s="229" t="n"/>
+      <c r="F16" s="229" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="49" t="inlineStr">
-        <is>
-          <t>제조사 / P/N</t>
-        </is>
-      </c>
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>핵심 정격</t>
-        </is>
-      </c>
-      <c r="C17" s="49" t="inlineStr">
-        <is>
-          <t>공급사</t>
-        </is>
-      </c>
-      <c r="D17" s="158" t="inlineStr">
-        <is>
-          <t>단가(USD)</t>
-        </is>
-      </c>
-      <c r="E17" s="49" t="inlineStr">
-        <is>
-          <t>가격 기준 수량</t>
-        </is>
-      </c>
-      <c r="F17" s="49" t="inlineStr">
-        <is>
-          <t>가격 확인일</t>
-        </is>
-      </c>
+      <c r="A17" s="190" t="inlineStr">
+        <is>
+          <t>검토 후보 MPN · 상세 정격·가격은 원본 Components에서 MPN으로 확인</t>
+        </is>
+      </c>
+      <c r="B17" s="248" t="n"/>
+      <c r="C17" s="248" t="n"/>
+      <c r="D17" s="248" t="n"/>
+      <c r="E17" s="248" t="n"/>
+      <c r="F17" s="249" t="n"/>
     </row>
     <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="89" t="inlineStr">
+      <c r="A18" s="242" t="inlineStr">
         <is>
           <t>{{manufacturer_part_number}}</t>
         </is>
       </c>
-      <c r="B18" s="90" t="inlineStr">
-        <is>
-          <t>{{key_spec}}</t>
-        </is>
-      </c>
-      <c r="C18" s="90" t="inlineStr">
-        <is>
-          <t>{{supplier}}</t>
-        </is>
-      </c>
-      <c r="D18" s="90" t="inlineStr">
-        <is>
-          <t>{{unit_price}}</t>
-        </is>
-      </c>
-      <c r="E18" s="90" t="inlineStr">
-        <is>
-          <t>{{price_basis}}</t>
-        </is>
-      </c>
-      <c r="F18" s="90" t="inlineStr">
-        <is>
-          <t>{{price_checked_at}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="50" customHeight="1"/>
+      <c r="B18" s="226" t="n"/>
+      <c r="C18" s="226" t="n"/>
+      <c r="D18" s="226" t="n"/>
+      <c r="E18" s="226" t="n"/>
+      <c r="F18" s="227" t="n"/>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="231" t="n"/>
+      <c r="B19" s="232" t="n"/>
+      <c r="C19" s="232" t="n"/>
+      <c r="D19" s="232" t="n"/>
+      <c r="E19" s="232" t="n"/>
+      <c r="F19" s="233" t="n"/>
+    </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="86" t="inlineStr">
         <is>
@@ -3045,36 +3697,37 @@
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="160" t="inlineStr">
+      <c r="A21" s="243" t="inlineStr">
         <is>
           <t>원본 {{source_file}}</t>
         </is>
       </c>
+      <c r="B21" s="229" t="n"/>
+      <c r="C21" s="229" t="n"/>
+      <c r="D21" s="229" t="n"/>
+      <c r="E21" s="229" t="n"/>
+      <c r="F21" s="229" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="22">
+  <mergeCells count="18">
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A18:F19"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:F11"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B9:D9"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="E9:F11"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C18:C19"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -3082,7 +3735,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 검토용&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 검토용&amp;C&amp;8 연녹색: 자동 | 연노랑: 수동&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
@@ -8,27 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대책서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="불량 근거" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부품 검토자료" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="reply_containment_scope">'대책서'!$C$18</definedName>
-    <definedName name="reply_containment">'대책서'!$C$19</definedName>
-    <definedName name="reply_root_cause_label">'대책서'!$C$20</definedName>
-    <definedName name="reply_root_cause">'대책서'!$C$21</definedName>
-    <definedName name="reply_escape_cause">'대책서'!$C$22</definedName>
-    <definedName name="reply_prevention">'대책서'!$C$23</definedName>
-    <definedName name="reply_verify_period">'대책서'!$C$25</definedName>
-    <definedName name="reply_verify_recipe">'대책서'!$E$25</definedName>
-    <definedName name="reply_verify_inspected">'대책서'!$G$25</definedName>
-    <definedName name="reply_verify_defective">'대책서'!$I$25</definedName>
-    <definedName name="reply_verify_status">'대책서'!$K$25</definedName>
-    <definedName name="reply_verify_note">'대책서'!$C$27</definedName>
-    <definedName name="reply_closed_at">'대책서'!$E$28</definedName>
-    <definedName name="reply_closure_note">'대책서'!$C$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$L$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'불량 근거'!$A$1:$E$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'부품 검토자료'!$A$1:$F$21</definedName>
+    <definedName name="reply_containment">'대책서'!$C$23</definedName>
+    <definedName name="reply_root_cause">'대책서'!$C$25</definedName>
+    <definedName name="reply_escape_cause">'대책서'!$C$27</definedName>
+    <definedName name="reply_prevention">'대책서'!$C$29</definedName>
+    <definedName name="reply_verify_note">'대책서'!$C$31</definedName>
+    <definedName name="reply_closed_at">'대책서'!$I$33</definedName>
+    <definedName name="reply_closure_note">'대책서'!$C$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$L$36</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -36,11 +25,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0&quot;배&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="67">
+  <fonts count="74">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -414,6 +405,45 @@
       <b val="1"/>
       <color rgb="00233D59"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="23"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="009C2A2A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00606060"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00606060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00606060"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="20">
@@ -514,7 +544,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -949,11 +979,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6ADB7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6ADB7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6ADB7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6ADB7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1628,6 +1672,78 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="42" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="3" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="9" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="13" borderId="42" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="13" borderId="42" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="13" borderId="42" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="42" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="43" fillId="13" borderId="42" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1760,250 +1876,13 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>User</author>
+    <author>MAIN_SERVER</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A19" authorId="0" shapeId="0">
       <text>
-        <t>부품 식별자: {{part_id}}</t>
-      </text>
-    </comment>
-    <comment ref="A4" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-시스템 자동 기입 · 발행 시점 고정  |  담당·기한·문서 상태는 관리자 갱신</t>
-      </text>
-    </comment>
-    <comment ref="C6" authorId="0" shapeId="0">
-      <text>
-        <t>제조사 P/N·정격·공급사 (이전 v2)
-{{datasheet_match}} · {{selected_mpn}}
-정격 {{selected_spec}} · 공급사 {{selected_supplier}}
-자세한 비교는 「부품 검토자료」 참조.</t>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t>시스템은 배정 대기만 초기 기입합니다. 실제 주관 담당자는 관리자가 작성합니다.</t>
-      </text>
-    </comment>
-    <comment ref="J7" authorId="0" shapeId="0">
-      <text>
-        <t>시스템은 담당자 입력만 초기 기입합니다. 실제 협조 부서는 관리자가 작성합니다.</t>
-      </text>
-    </comment>
-    <comment ref="A9" authorId="0" shapeId="0">
-      <text>
-        <t>문서 상태와 회신 기한은 시스템이 ISSUED / 담당자 입력으로 초기화하며 이후 관리자가 갱신합니다. Job 상태 또는 DB의 메일 전송 상태와 별개입니다.
-이전 v2 내용(참고):
-상태 {{alert_status}} · 발행 기준 {{vs_threshold_ratio}}
-회신 ① {{due_initial}}   ②③ {{due_cause}}   ④ {{due_action}}   ⑤⑥ {{due_verify}}</t>
-      </text>
-    </comment>
-    <comment ref="A12" authorId="0" shapeId="0">
-      <text>
-        <t>실제 발주·입고 자료로 확인한 업체명. 데이터시트 공급사를 자동 전사하지 않습니다.</t>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
-      <text>
-        <t>업체 담당자·직책·연락처. 접수 확인은 불량 근거에 기록합니다.</t>
-      </text>
-    </comment>
-    <comment ref="I12" authorId="0" shapeId="0">
-      <text>
-        <t>요청 마감 일시와 시간대. 원인·대책 기한은 초동 조치 칸에 기록합니다.</t>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
-      <text>
-        <t>시스템 자동 기입. 동일 Job 시작(없으면 요청) 시각부터 대상 검사 시각까지 누적 집계합니다. 기간 일수: {{window_days}}. 이동 7일 집계가 아닙니다.</t>
-      </text>
-    </comment>
-    <comment ref="A14" authorId="0" shapeId="0">
-      <text>
-        <t>동일 Job·부품·불량 유형, 대상 검사 시점까지 누적. 검사 수량은 검사 Unit 수 × 부품 슬롯 수. 폐기 수량이나 납품 Lot 불량률이 아닙니다.</t>
-      </text>
-    </comment>
-    <comment ref="A15" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-자동 분석</t>
-      </text>
-    </comment>
-    <comment ref="A17" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-관리자 직접 작성  |  ①~⑥ 조치·원인·대책·검증·종결</t>
-      </text>
-    </comment>
-    <comment ref="A18" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-① 초동 조치</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-□ 생산 중단    □ 출하 보류    □ 재고 선별    □ 고객 통보    □ 설비 정지</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>당사 담당자가 작성: 조치 요청 범위 / 실제 실행 시각·확인자 / 확정·의심 수량 구분 / 초기·원인·대책 회신 마감 / 관련 문서번호. 자동 정지 완료로 해석하지 않습니다.</t>
-      </text>
-    </comment>
-    <comment ref="A20" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-② 발생 원인</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>② 발생 원인의 핵심을 한 줄로 요약합니다.</t>
-      </text>
-    </comment>
-    <comment ref="C21" authorId="0" shapeId="0">
-      <text>
-        <t>거래처 또는 조치부서 회신: 발생 원인 + 재현·비교 시험 근거 + 책임 판단. 추정과 입증을 구분합니다.</t>
-      </text>
-    </comment>
-    <comment ref="A22" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-③ 유출 원인</t>
-      </text>
-    </comment>
-    <comment ref="C22" authorId="0" shapeId="0">
-      <text>
-        <t>왜 기존 검사에서 발견하지 못했는지, 해당 검사 기준·검출 능력과 입증 자료를 적습니다.</t>
-      </text>
-    </comment>
-    <comment ref="A23" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-④ 재발방지
-대책</t>
-      </text>
-    </comment>
-    <comment ref="C23" authorId="0" shapeId="0">
-      <text>
-        <t>변경 내용, 담당자, 완료 예정·실제 일시, 적용 Lot 또는 Unit, 변경 승인·효과 검증 자료 번호.</t>
-      </text>
-    </comment>
-    <comment ref="A24" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-⑤ 효과 검증</t>
-      </text>
-    </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-불량률(자동 계산)</t>
-      </text>
-    </comment>
-    <comment ref="F26" authorId="0" shapeId="0">
-      <text>
-        <t>자동 계산. 검증 불량 수량 ÷ 검증 검사 수량. 검증 수량은 부품 검사 건수 기준입니다.</t>
-      </text>
-    </comment>
-    <comment ref="H26" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-검증 수량: 부품 검사 건수 기준</t>
-      </text>
-    </comment>
-    <comment ref="A28" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-⑥ 종결</t>
-      </text>
-    </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-잔여 위험 · 이관 사항 확인</t>
-      </text>
-    </comment>
-    <comment ref="A30" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-노랑: 관리자 작성 · 파랑: 자동 계산 · 그 외: 시스템 기입 / 입력 칸 클릭 시 작성 안내</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>User</author>
-  </authors>
-  <commentList>
-    <comment ref="B10" authorId="0" shapeId="0">
-      <text>
-        <t>적용 규격·개정 / 허용 기준 / 실측값 / 시험·사진 번호</t>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
-      <text>
-        <t>실제 납품업체 / PO·납품 번호 / 제조 Lot·Date Code / 입고일</t>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0" shapeId="0">
-      <text>
-        <t>확정 불량 / 의심 수량 / 재고·공정품·기출하 / 격리 위치</t>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
-      <text>
-        <t>기판 기능 결과 / 재작업·폐기 판정 / 근거 번호</t>
-      </text>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0">
-      <text>
-        <t>통보·접수 확인 일시 / 실제 회신 일시 / 관련 대책서 번호</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
-      <text>
-        <t>정지·재개 확인자와 시각 / 공수·폐기 수량 / 비용 증빙</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>User</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-부품 검토자료 · 시스템 자동 기입</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>데이터시트의 공급사 정보입니다. 해당 불량품의 실제 납품업체·귀책과 연결되지 않습니다.</t>
-      </text>
-    </comment>
-    <comment ref="A12" authorId="0" shapeId="0">
-      <text>
-        <t>이전 v2 내용(참고):
-Checklist 공통·부품별 항목을 함께 조회 · 원인·적합성 판단은 관리자 작성</t>
-      </text>
-    </comment>
-    <comment ref="A18" authorId="0" shapeId="0">
-      <text>
-        <t>같은 부품 타입의 후보 목록이며 대체 승인 목록이 아닙니다. 원본 데이터시트에서 MPN별 정격·공급사·가격을 확인합니다.</t>
+        <t>검사 이미지 경로: {{inspection_image_path}}
+SHA-256: {{inspection_image_sha256}}</t>
       </text>
     </comment>
   </commentList>
@@ -2014,10 +1893,10 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
+      <col>6</col>
+      <colOff>152400</colOff>
+      <row>14</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="2857500" cy="1609725"/>
     <pic>
@@ -2033,19 +1912,16 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
+      <col>6</col>
+      <colOff>152400</colOff>
+      <row>14</row>
+      <rowOff>28575</rowOff>
     </from>
     <ext cx="2857500" cy="1609725"/>
     <pic>
@@ -2061,9 +1937,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2357,1390 +2230,767 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00233D59"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <outlinePr summaryBelow="1" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6.4" customWidth="1" min="1" max="1"/>
-    <col width="6.4" customWidth="1" min="2" max="2"/>
-    <col width="6.4" customWidth="1" min="3" max="3"/>
-    <col width="6.4" customWidth="1" min="4" max="4"/>
-    <col width="6.4" customWidth="1" min="5" max="5"/>
-    <col width="6.4" customWidth="1" min="6" max="6"/>
-    <col width="6.4" customWidth="1" min="7" max="7"/>
-    <col width="6.4" customWidth="1" min="8" max="8"/>
-    <col width="6.4" customWidth="1" min="9" max="9"/>
-    <col width="6.4" customWidth="1" min="10" max="10"/>
-    <col width="6.4" customWidth="1" min="11" max="11"/>
-    <col width="6.4" customWidth="1" min="12" max="12"/>
+    <col width="7.4" customWidth="1" min="1" max="1"/>
+    <col width="7.4" customWidth="1" min="2" max="2"/>
+    <col width="7.4" customWidth="1" min="3" max="3"/>
+    <col width="7.4" customWidth="1" min="4" max="4"/>
+    <col width="7.4" customWidth="1" min="5" max="5"/>
+    <col width="7.4" customWidth="1" min="6" max="6"/>
+    <col width="7.4" customWidth="1" min="7" max="7"/>
+    <col width="7.4" customWidth="1" min="8" max="8"/>
+    <col width="7.4" customWidth="1" min="9" max="9"/>
+    <col width="7.4" customWidth="1" min="10" max="10"/>
+    <col width="7.4" customWidth="1" min="11" max="11"/>
+    <col width="7.4" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" s="161" t="inlineStr">
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="252" t="inlineStr">
         <is>
           <t>불 량 대 책 서</t>
         </is>
       </c>
-      <c r="G1" s="122" t="inlineStr">
+      <c r="B1" s="253" t="n"/>
+      <c r="C1" s="253" t="n"/>
+      <c r="D1" s="253" t="n"/>
+      <c r="E1" s="253" t="n"/>
+      <c r="F1" s="253" t="n"/>
+      <c r="G1" s="253" t="n"/>
+      <c r="H1" s="253" t="n"/>
+      <c r="I1" s="254" t="inlineStr">
         <is>
           <t>작성</t>
         </is>
       </c>
-      <c r="H1" s="123" t="n"/>
-      <c r="I1" s="122" t="inlineStr">
-        <is>
-          <t>검토</t>
-        </is>
-      </c>
-      <c r="J1" s="123" t="n"/>
-      <c r="K1" s="122" t="inlineStr">
+      <c r="J1" s="255" t="n"/>
+      <c r="K1" s="254" t="inlineStr">
         <is>
           <t>승인</t>
         </is>
       </c>
-      <c r="L1" s="123" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="G2" s="195" t="n"/>
-      <c r="H2" s="162" t="n"/>
-      <c r="I2" s="195" t="n"/>
-      <c r="J2" s="162" t="n"/>
-      <c r="K2" s="195" t="n"/>
-      <c r="L2" s="162" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="G3" s="163" t="n"/>
-      <c r="H3" s="164" t="n"/>
-      <c r="I3" s="163" t="n"/>
-      <c r="J3" s="164" t="n"/>
-      <c r="K3" s="163" t="n"/>
-      <c r="L3" s="164" t="n"/>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="199" t="inlineStr">
-        <is>
-          <t>01  발생 사실 · 시스템 자동 기입  |  확정 불량 개별 건 발행</t>
-        </is>
-      </c>
+      <c r="L1" s="255" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="253" t="n"/>
+      <c r="B2" s="253" t="n"/>
+      <c r="C2" s="253" t="n"/>
+      <c r="D2" s="253" t="n"/>
+      <c r="E2" s="253" t="n"/>
+      <c r="F2" s="253" t="n"/>
+      <c r="G2" s="253" t="n"/>
+      <c r="H2" s="253" t="n"/>
+      <c r="I2" s="256" t="n"/>
+      <c r="J2" s="257" t="n"/>
+      <c r="K2" s="256" t="n"/>
+      <c r="L2" s="257" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="253" t="n"/>
+      <c r="B3" s="253" t="n"/>
+      <c r="C3" s="253" t="n"/>
+      <c r="D3" s="253" t="n"/>
+      <c r="E3" s="253" t="n"/>
+      <c r="F3" s="253" t="n"/>
+      <c r="G3" s="253" t="n"/>
+      <c r="H3" s="253" t="n"/>
+      <c r="I3" s="257" t="n"/>
+      <c r="J3" s="257" t="n"/>
+      <c r="K3" s="257" t="n"/>
+      <c r="L3" s="257" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="258" t="inlineStr">
+        <is>
+          <t>01  발생 정보</t>
+        </is>
+      </c>
+      <c r="B4" s="259" t="n"/>
+      <c r="C4" s="259" t="n"/>
+      <c r="D4" s="259" t="n"/>
+      <c r="E4" s="259" t="n"/>
+      <c r="F4" s="259" t="n"/>
+      <c r="G4" s="259" t="n"/>
+      <c r="H4" s="259" t="n"/>
+      <c r="I4" s="259" t="n"/>
+      <c r="J4" s="259" t="n"/>
+      <c r="K4" s="259" t="n"/>
+      <c r="L4" s="259" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="122" t="inlineStr">
+      <c r="A5" s="260" t="inlineStr">
         <is>
           <t>문서번호</t>
         </is>
       </c>
-      <c r="B5" s="123" t="n"/>
-      <c r="C5" s="200" t="inlineStr">
+      <c r="B5" s="255" t="n"/>
+      <c r="C5" s="261" t="inlineStr">
         <is>
           <t>{{alert_code}}</t>
         </is>
       </c>
-      <c r="D5" s="130" t="n"/>
-      <c r="E5" s="130" t="n"/>
-      <c r="F5" s="130" t="n"/>
-      <c r="G5" s="123" t="n"/>
-      <c r="H5" s="122" t="inlineStr">
+      <c r="D5" s="262" t="n"/>
+      <c r="E5" s="262" t="n"/>
+      <c r="F5" s="262" t="n"/>
+      <c r="G5" s="262" t="n"/>
+      <c r="H5" s="262" t="n"/>
+      <c r="I5" s="260" t="inlineStr">
+        <is>
+          <t>문서 상태</t>
+        </is>
+      </c>
+      <c r="J5" s="255" t="n"/>
+      <c r="K5" s="263" t="inlineStr">
+        <is>
+          <t>발행</t>
+        </is>
+      </c>
+      <c r="L5" s="257" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="260" t="inlineStr">
+        <is>
+          <t>대상 부품</t>
+        </is>
+      </c>
+      <c r="B6" s="255" t="n"/>
+      <c r="C6" s="264" t="inlineStr">
+        <is>
+          <t>{{part_id}} · {{part_name}} ({{category_label}})</t>
+        </is>
+      </c>
+      <c r="D6" s="262" t="n"/>
+      <c r="E6" s="262" t="n"/>
+      <c r="F6" s="262" t="n"/>
+      <c r="G6" s="262" t="n"/>
+      <c r="H6" s="262" t="n"/>
+      <c r="I6" s="262" t="n"/>
+      <c r="J6" s="262" t="n"/>
+      <c r="K6" s="262" t="n"/>
+      <c r="L6" s="262" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="260" t="inlineStr">
+        <is>
+          <t>발생 대상</t>
+        </is>
+      </c>
+      <c r="B7" s="255" t="n"/>
+      <c r="C7" s="265" t="inlineStr">
+        <is>
+          <t>Job {{job_id}}
+Unit {{target_unit_id}} · 슬롯 {{target_slot_code}} · 불량 ID {{unit_defect_id}}</t>
+        </is>
+      </c>
+      <c r="D7" s="262" t="n"/>
+      <c r="E7" s="262" t="n"/>
+      <c r="F7" s="262" t="n"/>
+      <c r="G7" s="262" t="n"/>
+      <c r="H7" s="262" t="n"/>
+      <c r="I7" s="262" t="n"/>
+      <c r="J7" s="262" t="n"/>
+      <c r="K7" s="262" t="n"/>
+      <c r="L7" s="262" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="260" t="inlineStr">
+        <is>
+          <t>검사일시</t>
+        </is>
+      </c>
+      <c r="B8" s="255" t="n"/>
+      <c r="C8" s="265" t="inlineStr">
+        <is>
+          <t>{{target_inspected_at}}</t>
+        </is>
+      </c>
+      <c r="D8" s="262" t="n"/>
+      <c r="E8" s="262" t="n"/>
+      <c r="F8" s="262" t="n"/>
+      <c r="G8" s="260" t="inlineStr">
         <is>
           <t>발행일시</t>
         </is>
       </c>
-      <c r="I5" s="123" t="n"/>
-      <c r="J5" s="203" t="inlineStr">
+      <c r="H8" s="255" t="n"/>
+      <c r="I8" s="265" t="inlineStr">
         <is>
           <t>{{issued_at}}</t>
         </is>
       </c>
-      <c r="K5" s="130" t="n"/>
-      <c r="L5" s="123" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="122" t="inlineStr">
-        <is>
-          <t>대상 부품</t>
-        </is>
-      </c>
-      <c r="B6" s="123" t="n"/>
-      <c r="C6" s="200" t="inlineStr">
-        <is>
-          <t>{{part_id}} · {{part_name}} ({{category_label}})</t>
-        </is>
-      </c>
-      <c r="D6" s="130" t="n"/>
-      <c r="E6" s="130" t="n"/>
-      <c r="F6" s="130" t="n"/>
-      <c r="G6" s="123" t="n"/>
-      <c r="H6" s="122" t="inlineStr">
+      <c r="J8" s="262" t="n"/>
+      <c r="K8" s="262" t="n"/>
+      <c r="L8" s="262" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="260" t="inlineStr">
         <is>
           <t>불량 유형</t>
         </is>
       </c>
-      <c r="I6" s="123" t="n"/>
-      <c r="J6" s="203" t="inlineStr">
+      <c r="B9" s="255" t="n"/>
+      <c r="C9" s="266" t="inlineStr">
         <is>
           <t>{{defect_type}}</t>
         </is>
       </c>
-      <c r="K6" s="130" t="n"/>
-      <c r="L6" s="123" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="122" t="inlineStr">
+      <c r="D9" s="262" t="n"/>
+      <c r="E9" s="262" t="n"/>
+      <c r="F9" s="262" t="n"/>
+      <c r="G9" s="260" t="inlineStr">
+        <is>
+          <t>발행 대상</t>
+        </is>
+      </c>
+      <c r="H9" s="255" t="n"/>
+      <c r="I9" s="267" t="inlineStr">
+        <is>
+          <t>확정 불량 1건</t>
+        </is>
+      </c>
+      <c r="J9" s="262" t="n"/>
+      <c r="K9" s="262" t="n"/>
+      <c r="L9" s="262" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="260" t="inlineStr">
         <is>
           <t>주관 담당</t>
         </is>
       </c>
-      <c r="B7" s="123" t="n"/>
-      <c r="C7" s="204" t="inlineStr">
+      <c r="B10" s="255" t="n"/>
+      <c r="C10" s="268" t="inlineStr">
         <is>
           <t>{{assignee}}</t>
         </is>
       </c>
-      <c r="D7" s="166" t="n"/>
-      <c r="E7" s="166" t="n"/>
-      <c r="F7" s="166" t="n"/>
-      <c r="G7" s="167" t="n"/>
-      <c r="H7" s="122" t="inlineStr">
-        <is>
-          <t>협조 부서</t>
-        </is>
-      </c>
-      <c r="I7" s="123" t="n"/>
-      <c r="J7" s="207" t="inlineStr">
-        <is>
-          <t>{{support_teams}}</t>
-        </is>
-      </c>
-      <c r="K7" s="166" t="n"/>
-      <c r="L7" s="167" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="122" t="inlineStr">
-        <is>
-          <t>발행 대상</t>
-        </is>
-      </c>
-      <c r="B8" s="123" t="n"/>
-      <c r="C8" s="208" t="inlineStr">
-        <is>
-          <t>Job {{job_id}}
-Unit {{target_unit_id}} · {{target_slot_code}}</t>
-        </is>
-      </c>
-      <c r="D8" s="130" t="n"/>
-      <c r="E8" s="130" t="n"/>
-      <c r="F8" s="130" t="n"/>
-      <c r="G8" s="123" t="n"/>
-      <c r="H8" s="122" t="inlineStr">
-        <is>
-          <t>검사 시각</t>
-        </is>
-      </c>
-      <c r="I8" s="123" t="n"/>
-      <c r="J8" s="203" t="inlineStr">
-        <is>
-          <t>{{target_inspected_at}}</t>
-        </is>
-      </c>
-      <c r="K8" s="130" t="n"/>
-      <c r="L8" s="123" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="169" t="inlineStr">
-        <is>
-          <t>문서 상태: 발행  |  확정 불량 1건 확인에 따른 통보 · 조치 실행 여부는 담당자 확인</t>
-        </is>
-      </c>
-      <c r="B9" s="166" t="n"/>
-      <c r="C9" s="166" t="n"/>
-      <c r="D9" s="166" t="n"/>
-      <c r="E9" s="166" t="n"/>
-      <c r="F9" s="166" t="n"/>
-      <c r="G9" s="166" t="n"/>
-      <c r="H9" s="166" t="n"/>
-      <c r="I9" s="166" t="n"/>
-      <c r="J9" s="166" t="n"/>
-      <c r="K9" s="166" t="n"/>
-      <c r="L9" s="167" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="172" t="inlineStr">
-        <is>
-          <t>02  실제 납품업체 · 당사 작성</t>
-        </is>
-      </c>
-      <c r="B11" s="209" t="n"/>
-      <c r="C11" s="209" t="n"/>
-      <c r="D11" s="210" t="n"/>
-      <c r="E11" s="172" t="inlineStr">
-        <is>
-          <t>거래처 회신 책임자 · 당사 작성</t>
-        </is>
-      </c>
-      <c r="F11" s="209" t="n"/>
-      <c r="G11" s="209" t="n"/>
-      <c r="H11" s="210" t="n"/>
-      <c r="I11" s="172" t="inlineStr">
-        <is>
-          <t>초기 회신 기한 · 당사 작성</t>
-        </is>
-      </c>
-      <c r="J11" s="209" t="n"/>
-      <c r="K11" s="209" t="n"/>
-      <c r="L11" s="210" t="n"/>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="173" t="inlineStr"/>
-      <c r="B12" s="244" t="n"/>
-      <c r="C12" s="244" t="n"/>
-      <c r="D12" s="245" t="n"/>
-      <c r="E12" s="174" t="inlineStr"/>
-      <c r="F12" s="244" t="n"/>
-      <c r="G12" s="244" t="n"/>
-      <c r="H12" s="245" t="n"/>
-      <c r="I12" s="174" t="inlineStr"/>
-      <c r="J12" s="244" t="n"/>
-      <c r="K12" s="244" t="n"/>
-      <c r="L12" s="245" t="n"/>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="122" t="inlineStr">
-        <is>
-          <t>집계 기간</t>
-        </is>
-      </c>
-      <c r="B13" s="123" t="n"/>
-      <c r="C13" s="213" t="inlineStr">
-        <is>
-          <t>{{period_start}}
-~ {{period_end}} ({{evaluation_mode}})</t>
-        </is>
-      </c>
-      <c r="D13" s="130" t="n"/>
-      <c r="E13" s="130" t="n"/>
-      <c r="F13" s="130" t="n"/>
-      <c r="G13" s="123" t="n"/>
-      <c r="H13" s="122" t="inlineStr">
-        <is>
-          <t>레시피</t>
-        </is>
-      </c>
-      <c r="I13" s="123" t="n"/>
-      <c r="J13" s="213" t="inlineStr">
-        <is>
-          <t>{{source_recipe_version}}</t>
-        </is>
-      </c>
-      <c r="K13" s="130" t="n"/>
-      <c r="L13" s="123" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="214" t="inlineStr">
-        <is>
-          <t>누적 참고 | 부품 검사 {{inspected_quantity}}건 · 불량 {{defective_quantity}}건 · {{defect_ppm}} PPM · 불량 Unit {{unit_impact}}</t>
-        </is>
-      </c>
-      <c r="B14" s="209" t="n"/>
-      <c r="C14" s="209" t="n"/>
-      <c r="D14" s="209" t="n"/>
-      <c r="E14" s="209" t="n"/>
-      <c r="F14" s="209" t="n"/>
-      <c r="G14" s="209" t="n"/>
-      <c r="H14" s="209" t="n"/>
-      <c r="I14" s="209" t="n"/>
-      <c r="J14" s="209" t="n"/>
-      <c r="K14" s="209" t="n"/>
-      <c r="L14" s="210" t="n"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="122" t="inlineStr">
-        <is>
-          <t>확인 사실</t>
-        </is>
-      </c>
-      <c r="B15" s="123" t="n"/>
-      <c r="C15" s="203" t="inlineStr">
-        <is>
-          <t>{{auto_analysis}}</t>
-        </is>
-      </c>
-      <c r="D15" s="130" t="n"/>
-      <c r="E15" s="130" t="n"/>
-      <c r="F15" s="130" t="n"/>
-      <c r="G15" s="130" t="n"/>
-      <c r="H15" s="130" t="n"/>
-      <c r="I15" s="130" t="n"/>
-      <c r="J15" s="130" t="n"/>
-      <c r="K15" s="130" t="n"/>
-      <c r="L15" s="123" t="n"/>
-    </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="217" t="inlineStr">
-        <is>
-          <t>03  조치 및 회신  |  당사 작성 → 거래처·조치부서 회신 → 당사 검증</t>
-        </is>
-      </c>
-      <c r="B17" s="130" t="n"/>
-      <c r="C17" s="130" t="n"/>
-      <c r="D17" s="130" t="n"/>
-      <c r="E17" s="130" t="n"/>
-      <c r="F17" s="130" t="n"/>
-      <c r="G17" s="130" t="n"/>
-      <c r="H17" s="130" t="n"/>
-      <c r="I17" s="130" t="n"/>
-      <c r="J17" s="130" t="n"/>
-      <c r="K17" s="130" t="n"/>
-      <c r="L17" s="123" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="122" t="inlineStr">
-        <is>
-          <t>① 당사
-초동·요청</t>
-        </is>
-      </c>
-      <c r="B18" s="144" t="n"/>
-      <c r="C18" s="218" t="inlineStr">
-        <is>
-          <t>요청  □ 생산 보류  □ 출하 보류  □ 격리·선별  □ 원인 분석  □ 기존 대책 연계</t>
-        </is>
-      </c>
-      <c r="D18" s="166" t="n"/>
-      <c r="E18" s="166" t="n"/>
-      <c r="F18" s="166" t="n"/>
-      <c r="G18" s="166" t="n"/>
-      <c r="H18" s="166" t="n"/>
-      <c r="I18" s="166" t="n"/>
-      <c r="J18" s="166" t="n"/>
-      <c r="K18" s="166" t="n"/>
-      <c r="L18" s="167" t="n"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="146" t="n"/>
-      <c r="B19" s="147" t="n"/>
-      <c r="C19" s="204" t="inlineStr"/>
-      <c r="D19" s="166" t="n"/>
-      <c r="E19" s="166" t="n"/>
-      <c r="F19" s="166" t="n"/>
-      <c r="G19" s="166" t="n"/>
-      <c r="H19" s="166" t="n"/>
-      <c r="I19" s="166" t="n"/>
-      <c r="J19" s="166" t="n"/>
-      <c r="K19" s="166" t="n"/>
-      <c r="L19" s="167" t="n"/>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="122" t="inlineStr">
-        <is>
-          <t>② 회신
-발생 원인</t>
-        </is>
-      </c>
-      <c r="B20" s="144" t="n"/>
-      <c r="C20" s="219" t="inlineStr"/>
-      <c r="D20" s="166" t="n"/>
-      <c r="E20" s="166" t="n"/>
-      <c r="F20" s="166" t="n"/>
-      <c r="G20" s="166" t="n"/>
-      <c r="H20" s="166" t="n"/>
-      <c r="I20" s="166" t="n"/>
-      <c r="J20" s="166" t="n"/>
-      <c r="K20" s="166" t="n"/>
-      <c r="L20" s="167" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="146" t="n"/>
-      <c r="B21" s="147" t="n"/>
-      <c r="C21" s="219" t="inlineStr"/>
-      <c r="D21" s="166" t="n"/>
-      <c r="E21" s="166" t="n"/>
-      <c r="F21" s="166" t="n"/>
-      <c r="G21" s="166" t="n"/>
-      <c r="H21" s="166" t="n"/>
-      <c r="I21" s="166" t="n"/>
-      <c r="J21" s="166" t="n"/>
-      <c r="K21" s="166" t="n"/>
-      <c r="L21" s="167" t="n"/>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="122" t="inlineStr">
-        <is>
-          <t>③ 회신
-유출 원인</t>
-        </is>
-      </c>
-      <c r="B22" s="123" t="n"/>
-      <c r="C22" s="219" t="inlineStr"/>
-      <c r="D22" s="166" t="n"/>
-      <c r="E22" s="166" t="n"/>
-      <c r="F22" s="166" t="n"/>
-      <c r="G22" s="166" t="n"/>
-      <c r="H22" s="166" t="n"/>
-      <c r="I22" s="166" t="n"/>
-      <c r="J22" s="166" t="n"/>
-      <c r="K22" s="166" t="n"/>
-      <c r="L22" s="167" t="n"/>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="122" t="inlineStr">
-        <is>
-          <t>④ 회신
-영구 대책</t>
-        </is>
-      </c>
-      <c r="B23" s="123" t="n"/>
-      <c r="C23" s="219" t="inlineStr"/>
-      <c r="D23" s="166" t="n"/>
-      <c r="E23" s="166" t="n"/>
-      <c r="F23" s="166" t="n"/>
-      <c r="G23" s="166" t="n"/>
-      <c r="H23" s="166" t="n"/>
-      <c r="I23" s="166" t="n"/>
-      <c r="J23" s="166" t="n"/>
-      <c r="K23" s="166" t="n"/>
-      <c r="L23" s="167" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="122" t="inlineStr">
-        <is>
-          <t>⑤ 당사
-효과 검증</t>
-        </is>
-      </c>
-      <c r="B24" s="144" t="n"/>
-      <c r="C24" s="122" t="inlineStr">
-        <is>
-          <t>검증 기간</t>
-        </is>
-      </c>
-      <c r="D24" s="123" t="n"/>
-      <c r="E24" s="122" t="inlineStr">
-        <is>
-          <t>적용 레시피</t>
-        </is>
-      </c>
-      <c r="F24" s="123" t="n"/>
-      <c r="G24" s="122" t="inlineStr">
-        <is>
-          <t>검사 수량</t>
-        </is>
-      </c>
-      <c r="H24" s="123" t="n"/>
-      <c r="I24" s="122" t="inlineStr">
-        <is>
-          <t>불량 수량</t>
-        </is>
-      </c>
-      <c r="J24" s="123" t="n"/>
-      <c r="K24" s="122" t="inlineStr">
-        <is>
-          <t>판정</t>
-        </is>
-      </c>
-      <c r="L24" s="123" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="149" t="n"/>
-      <c r="B25" s="150" t="n"/>
-      <c r="C25" s="220" t="n"/>
-      <c r="D25" s="167" t="n"/>
-      <c r="E25" s="220" t="n"/>
-      <c r="F25" s="167" t="n"/>
-      <c r="G25" s="221" t="n"/>
-      <c r="H25" s="167" t="n"/>
-      <c r="I25" s="221" t="n"/>
-      <c r="J25" s="167" t="n"/>
-      <c r="K25" s="220" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="L25" s="167" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="149" t="n"/>
-      <c r="B26" s="150" t="n"/>
-      <c r="C26" s="122" t="inlineStr">
-        <is>
-          <t>불량률 · 자동 계산</t>
-        </is>
-      </c>
-      <c r="D26" s="130" t="n"/>
-      <c r="E26" s="123" t="n"/>
-      <c r="F26" s="222">
-        <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),I25/G25,"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="123" t="n"/>
-      <c r="H26" s="223">
-        <f>IF(AND(ISNUMBER(G25),ISNUMBER(I25),G25&gt;0),"검증 PPM  "&amp;TEXT(I25/G25*1000000,"#,##0"),"검증 PPM  —")</f>
-        <v/>
-      </c>
-      <c r="I26" s="130" t="n"/>
-      <c r="J26" s="130" t="n"/>
-      <c r="K26" s="130" t="n"/>
-      <c r="L26" s="123" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="146" t="n"/>
-      <c r="B27" s="147" t="n"/>
-      <c r="C27" s="204" t="inlineStr"/>
-      <c r="D27" s="166" t="n"/>
-      <c r="E27" s="166" t="n"/>
-      <c r="F27" s="166" t="n"/>
-      <c r="G27" s="166" t="n"/>
-      <c r="H27" s="166" t="n"/>
-      <c r="I27" s="166" t="n"/>
-      <c r="J27" s="166" t="n"/>
-      <c r="K27" s="166" t="n"/>
-      <c r="L27" s="167" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="122" t="inlineStr">
-        <is>
-          <t>⑥ 당사
-승인·종결</t>
-        </is>
-      </c>
-      <c r="B28" s="144" t="n"/>
-      <c r="C28" s="122" t="inlineStr">
+      <c r="D10" s="257" t="n"/>
+      <c r="E10" s="257" t="n"/>
+      <c r="F10" s="257" t="n"/>
+      <c r="G10" s="260" t="inlineStr">
+        <is>
+          <t>초기 회신</t>
+        </is>
+      </c>
+      <c r="H10" s="255" t="n"/>
+      <c r="I10" s="269" t="n"/>
+      <c r="J10" s="257" t="n"/>
+      <c r="K10" s="257" t="n"/>
+      <c r="L10" s="257" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="260" t="inlineStr">
+        <is>
+          <t>납품 추적</t>
+        </is>
+      </c>
+      <c r="B11" s="255" t="n"/>
+      <c r="C11" s="270" t="n"/>
+      <c r="D11" s="257" t="n"/>
+      <c r="E11" s="257" t="n"/>
+      <c r="F11" s="257" t="n"/>
+      <c r="G11" s="257" t="n"/>
+      <c r="H11" s="257" t="n"/>
+      <c r="I11" s="257" t="n"/>
+      <c r="J11" s="257" t="n"/>
+      <c r="K11" s="257" t="n"/>
+      <c r="L11" s="257" t="n"/>
+    </row>
+    <row r="12" ht="5" customHeight="1">
+      <c r="A12" s="271" t="n"/>
+      <c r="B12" s="271" t="n"/>
+      <c r="C12" s="271" t="n"/>
+      <c r="D12" s="271" t="n"/>
+      <c r="E12" s="271" t="n"/>
+      <c r="F12" s="271" t="n"/>
+      <c r="G12" s="271" t="n"/>
+      <c r="H12" s="271" t="n"/>
+      <c r="I12" s="271" t="n"/>
+      <c r="J12" s="271" t="n"/>
+      <c r="K12" s="271" t="n"/>
+      <c r="L12" s="271" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="272" t="inlineStr">
+        <is>
+          <t>02  불량 현상 및 판정 근거</t>
+        </is>
+      </c>
+      <c r="B13" s="273" t="n"/>
+      <c r="C13" s="273" t="n"/>
+      <c r="D13" s="273" t="n"/>
+      <c r="E13" s="273" t="n"/>
+      <c r="F13" s="273" t="n"/>
+      <c r="G13" s="273" t="n"/>
+      <c r="H13" s="273" t="n"/>
+      <c r="I13" s="273" t="n"/>
+      <c r="J13" s="273" t="n"/>
+      <c r="K13" s="273" t="n"/>
+      <c r="L13" s="273" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="254" t="inlineStr">
+        <is>
+          <t>확인 사실 · 판정 근거</t>
+        </is>
+      </c>
+      <c r="B14" s="255" t="n"/>
+      <c r="C14" s="255" t="n"/>
+      <c r="D14" s="255" t="n"/>
+      <c r="E14" s="255" t="n"/>
+      <c r="F14" s="255" t="n"/>
+      <c r="G14" s="254" t="inlineStr">
+        <is>
+          <t>해당 검사 이미지</t>
+        </is>
+      </c>
+      <c r="H14" s="255" t="n"/>
+      <c r="I14" s="255" t="n"/>
+      <c r="J14" s="255" t="n"/>
+      <c r="K14" s="255" t="n"/>
+      <c r="L14" s="255" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="264" t="inlineStr">
+        <is>
+          <t>Unit {{target_unit_id}} / {{target_slot_code}}에서
+{{defect_type}}이 확인됨.</t>
+        </is>
+      </c>
+      <c r="B15" s="262" t="n"/>
+      <c r="C15" s="262" t="n"/>
+      <c r="D15" s="262" t="n"/>
+      <c r="E15" s="262" t="n"/>
+      <c r="F15" s="262" t="n"/>
+      <c r="G15" s="274" t="n"/>
+      <c r="H15" s="262" t="n"/>
+      <c r="I15" s="262" t="n"/>
+      <c r="J15" s="262" t="n"/>
+      <c r="K15" s="262" t="n"/>
+      <c r="L15" s="262" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="262" t="n"/>
+      <c r="B16" s="262" t="n"/>
+      <c r="C16" s="262" t="n"/>
+      <c r="D16" s="262" t="n"/>
+      <c r="E16" s="262" t="n"/>
+      <c r="F16" s="262" t="n"/>
+      <c r="G16" s="262" t="n"/>
+      <c r="H16" s="262" t="n"/>
+      <c r="I16" s="262" t="n"/>
+      <c r="J16" s="262" t="n"/>
+      <c r="K16" s="262" t="n"/>
+      <c r="L16" s="262" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="254" t="inlineStr">
+        <is>
+          <t>판정 근거</t>
+        </is>
+      </c>
+      <c r="B17" s="255" t="n"/>
+      <c r="C17" s="270" t="n"/>
+      <c r="D17" s="257" t="n"/>
+      <c r="E17" s="257" t="n"/>
+      <c r="F17" s="257" t="n"/>
+      <c r="G17" s="262" t="n"/>
+      <c r="H17" s="262" t="n"/>
+      <c r="I17" s="262" t="n"/>
+      <c r="J17" s="262" t="n"/>
+      <c r="K17" s="262" t="n"/>
+      <c r="L17" s="262" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="255" t="n"/>
+      <c r="B18" s="255" t="n"/>
+      <c r="C18" s="257" t="n"/>
+      <c r="D18" s="257" t="n"/>
+      <c r="E18" s="257" t="n"/>
+      <c r="F18" s="257" t="n"/>
+      <c r="G18" s="262" t="n"/>
+      <c r="H18" s="262" t="n"/>
+      <c r="I18" s="262" t="n"/>
+      <c r="J18" s="262" t="n"/>
+      <c r="K18" s="262" t="n"/>
+      <c r="L18" s="262" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="275" t="inlineStr">
+        <is>
+          <t>{{inspection_image_status}}</t>
+        </is>
+      </c>
+      <c r="B19" s="262" t="n"/>
+      <c r="C19" s="262" t="n"/>
+      <c r="D19" s="262" t="n"/>
+      <c r="E19" s="262" t="n"/>
+      <c r="F19" s="262" t="n"/>
+      <c r="G19" s="262" t="n"/>
+      <c r="H19" s="262" t="n"/>
+      <c r="I19" s="262" t="n"/>
+      <c r="J19" s="262" t="n"/>
+      <c r="K19" s="262" t="n"/>
+      <c r="L19" s="262" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="262" t="n"/>
+      <c r="B20" s="262" t="n"/>
+      <c r="C20" s="262" t="n"/>
+      <c r="D20" s="262" t="n"/>
+      <c r="E20" s="262" t="n"/>
+      <c r="F20" s="262" t="n"/>
+      <c r="G20" s="262" t="n"/>
+      <c r="H20" s="262" t="n"/>
+      <c r="I20" s="262" t="n"/>
+      <c r="J20" s="262" t="n"/>
+      <c r="K20" s="262" t="n"/>
+      <c r="L20" s="262" t="n"/>
+    </row>
+    <row r="21" ht="5" customHeight="1">
+      <c r="A21" s="271" t="n"/>
+      <c r="B21" s="271" t="n"/>
+      <c r="C21" s="271" t="n"/>
+      <c r="D21" s="271" t="n"/>
+      <c r="E21" s="271" t="n"/>
+      <c r="F21" s="271" t="n"/>
+      <c r="G21" s="271" t="n"/>
+      <c r="H21" s="271" t="n"/>
+      <c r="I21" s="271" t="n"/>
+      <c r="J21" s="271" t="n"/>
+      <c r="K21" s="271" t="n"/>
+      <c r="L21" s="271" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="258" t="inlineStr">
+        <is>
+          <t>03  조치 · 효과 확인 · 종결</t>
+        </is>
+      </c>
+      <c r="B22" s="259" t="n"/>
+      <c r="C22" s="259" t="n"/>
+      <c r="D22" s="259" t="n"/>
+      <c r="E22" s="259" t="n"/>
+      <c r="F22" s="259" t="n"/>
+      <c r="G22" s="259" t="n"/>
+      <c r="H22" s="259" t="n"/>
+      <c r="I22" s="259" t="n"/>
+      <c r="J22" s="259" t="n"/>
+      <c r="K22" s="259" t="n"/>
+      <c r="L22" s="259" t="n"/>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="260" t="inlineStr">
+        <is>
+          <t>초동조치</t>
+        </is>
+      </c>
+      <c r="B23" s="255" t="n"/>
+      <c r="C23" s="270" t="n"/>
+      <c r="D23" s="257" t="n"/>
+      <c r="E23" s="257" t="n"/>
+      <c r="F23" s="257" t="n"/>
+      <c r="G23" s="257" t="n"/>
+      <c r="H23" s="257" t="n"/>
+      <c r="I23" s="257" t="n"/>
+      <c r="J23" s="257" t="n"/>
+      <c r="K23" s="257" t="n"/>
+      <c r="L23" s="257" t="n"/>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="255" t="n"/>
+      <c r="B24" s="255" t="n"/>
+      <c r="C24" s="257" t="n"/>
+      <c r="D24" s="257" t="n"/>
+      <c r="E24" s="257" t="n"/>
+      <c r="F24" s="257" t="n"/>
+      <c r="G24" s="257" t="n"/>
+      <c r="H24" s="257" t="n"/>
+      <c r="I24" s="257" t="n"/>
+      <c r="J24" s="257" t="n"/>
+      <c r="K24" s="257" t="n"/>
+      <c r="L24" s="257" t="n"/>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="260" t="inlineStr">
+        <is>
+          <t>발생 원인</t>
+        </is>
+      </c>
+      <c r="B25" s="255" t="n"/>
+      <c r="C25" s="270" t="n"/>
+      <c r="D25" s="257" t="n"/>
+      <c r="E25" s="257" t="n"/>
+      <c r="F25" s="257" t="n"/>
+      <c r="G25" s="257" t="n"/>
+      <c r="H25" s="257" t="n"/>
+      <c r="I25" s="257" t="n"/>
+      <c r="J25" s="257" t="n"/>
+      <c r="K25" s="257" t="n"/>
+      <c r="L25" s="257" t="n"/>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="255" t="n"/>
+      <c r="B26" s="255" t="n"/>
+      <c r="C26" s="257" t="n"/>
+      <c r="D26" s="257" t="n"/>
+      <c r="E26" s="257" t="n"/>
+      <c r="F26" s="257" t="n"/>
+      <c r="G26" s="257" t="n"/>
+      <c r="H26" s="257" t="n"/>
+      <c r="I26" s="257" t="n"/>
+      <c r="J26" s="257" t="n"/>
+      <c r="K26" s="257" t="n"/>
+      <c r="L26" s="257" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="260" t="inlineStr">
+        <is>
+          <t>유출 원인</t>
+        </is>
+      </c>
+      <c r="B27" s="255" t="n"/>
+      <c r="C27" s="270" t="n"/>
+      <c r="D27" s="257" t="n"/>
+      <c r="E27" s="257" t="n"/>
+      <c r="F27" s="257" t="n"/>
+      <c r="G27" s="257" t="n"/>
+      <c r="H27" s="257" t="n"/>
+      <c r="I27" s="257" t="n"/>
+      <c r="J27" s="257" t="n"/>
+      <c r="K27" s="257" t="n"/>
+      <c r="L27" s="257" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="255" t="n"/>
+      <c r="B28" s="255" t="n"/>
+      <c r="C28" s="257" t="n"/>
+      <c r="D28" s="257" t="n"/>
+      <c r="E28" s="257" t="n"/>
+      <c r="F28" s="257" t="n"/>
+      <c r="G28" s="257" t="n"/>
+      <c r="H28" s="257" t="n"/>
+      <c r="I28" s="257" t="n"/>
+      <c r="J28" s="257" t="n"/>
+      <c r="K28" s="257" t="n"/>
+      <c r="L28" s="257" t="n"/>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="260" t="inlineStr">
+        <is>
+          <t>재발방지</t>
+        </is>
+      </c>
+      <c r="B29" s="255" t="n"/>
+      <c r="C29" s="270" t="n"/>
+      <c r="D29" s="257" t="n"/>
+      <c r="E29" s="257" t="n"/>
+      <c r="F29" s="257" t="n"/>
+      <c r="G29" s="257" t="n"/>
+      <c r="H29" s="257" t="n"/>
+      <c r="I29" s="257" t="n"/>
+      <c r="J29" s="257" t="n"/>
+      <c r="K29" s="257" t="n"/>
+      <c r="L29" s="257" t="n"/>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="255" t="n"/>
+      <c r="B30" s="255" t="n"/>
+      <c r="C30" s="257" t="n"/>
+      <c r="D30" s="257" t="n"/>
+      <c r="E30" s="257" t="n"/>
+      <c r="F30" s="257" t="n"/>
+      <c r="G30" s="257" t="n"/>
+      <c r="H30" s="257" t="n"/>
+      <c r="I30" s="257" t="n"/>
+      <c r="J30" s="257" t="n"/>
+      <c r="K30" s="257" t="n"/>
+      <c r="L30" s="257" t="n"/>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="260" t="inlineStr">
+        <is>
+          <t>효과 확인</t>
+        </is>
+      </c>
+      <c r="B31" s="255" t="n"/>
+      <c r="C31" s="270" t="n"/>
+      <c r="D31" s="257" t="n"/>
+      <c r="E31" s="257" t="n"/>
+      <c r="F31" s="257" t="n"/>
+      <c r="G31" s="257" t="n"/>
+      <c r="H31" s="257" t="n"/>
+      <c r="I31" s="257" t="n"/>
+      <c r="J31" s="257" t="n"/>
+      <c r="K31" s="257" t="n"/>
+      <c r="L31" s="257" t="n"/>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="255" t="n"/>
+      <c r="B32" s="255" t="n"/>
+      <c r="C32" s="257" t="n"/>
+      <c r="D32" s="257" t="n"/>
+      <c r="E32" s="257" t="n"/>
+      <c r="F32" s="257" t="n"/>
+      <c r="G32" s="257" t="n"/>
+      <c r="H32" s="257" t="n"/>
+      <c r="I32" s="257" t="n"/>
+      <c r="J32" s="257" t="n"/>
+      <c r="K32" s="257" t="n"/>
+      <c r="L32" s="257" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="260" t="inlineStr">
+        <is>
+          <t>확인자</t>
+        </is>
+      </c>
+      <c r="B33" s="255" t="n"/>
+      <c r="C33" s="268" t="n"/>
+      <c r="D33" s="257" t="n"/>
+      <c r="E33" s="257" t="n"/>
+      <c r="F33" s="257" t="n"/>
+      <c r="G33" s="260" t="inlineStr">
         <is>
           <t>종결일</t>
         </is>
       </c>
-      <c r="D28" s="123" t="n"/>
-      <c r="E28" s="204" t="n"/>
-      <c r="F28" s="166" t="n"/>
-      <c r="G28" s="167" t="n"/>
-      <c r="H28" s="154" t="inlineStr">
-        <is>
-          <t>재개·출하 승인 및 잔여 사항</t>
-        </is>
-      </c>
-      <c r="I28" s="130" t="n"/>
-      <c r="J28" s="130" t="n"/>
-      <c r="K28" s="130" t="n"/>
-      <c r="L28" s="123" t="n"/>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="146" t="n"/>
-      <c r="B29" s="147" t="n"/>
-      <c r="C29" s="204" t="inlineStr"/>
-      <c r="D29" s="166" t="n"/>
-      <c r="E29" s="166" t="n"/>
-      <c r="F29" s="166" t="n"/>
-      <c r="G29" s="166" t="n"/>
-      <c r="H29" s="166" t="n"/>
-      <c r="I29" s="166" t="n"/>
-      <c r="J29" s="166" t="n"/>
-      <c r="K29" s="166" t="n"/>
-      <c r="L29" s="167" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="185" t="inlineStr">
-        <is>
-          <t>연녹색: 자동 기입·자동 계산  |  연노랑: 수동 작성(당사·거래처)</t>
-        </is>
-      </c>
+      <c r="H33" s="255" t="n"/>
+      <c r="I33" s="276" t="n"/>
+      <c r="J33" s="257" t="n"/>
+      <c r="K33" s="257" t="n"/>
+      <c r="L33" s="257" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="260" t="inlineStr">
+        <is>
+          <t>종결 판정</t>
+        </is>
+      </c>
+      <c r="B34" s="255" t="n"/>
+      <c r="C34" s="270" t="n"/>
+      <c r="D34" s="257" t="n"/>
+      <c r="E34" s="257" t="n"/>
+      <c r="F34" s="257" t="n"/>
+      <c r="G34" s="257" t="n"/>
+      <c r="H34" s="257" t="n"/>
+      <c r="I34" s="257" t="n"/>
+      <c r="J34" s="257" t="n"/>
+      <c r="K34" s="257" t="n"/>
+      <c r="L34" s="257" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="255" t="n"/>
+      <c r="B35" s="255" t="n"/>
+      <c r="C35" s="257" t="n"/>
+      <c r="D35" s="257" t="n"/>
+      <c r="E35" s="257" t="n"/>
+      <c r="F35" s="257" t="n"/>
+      <c r="G35" s="257" t="n"/>
+      <c r="H35" s="257" t="n"/>
+      <c r="I35" s="257" t="n"/>
+      <c r="J35" s="257" t="n"/>
+      <c r="K35" s="257" t="n"/>
+      <c r="L35" s="257" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="277" t="inlineStr">
+        <is>
+          <t>노란 칸: 담당자 작성 · 원인·조치·효과는 확인 후 기록</t>
+        </is>
+      </c>
+      <c r="B36" s="253" t="n"/>
+      <c r="C36" s="253" t="n"/>
+      <c r="D36" s="253" t="n"/>
+      <c r="E36" s="253" t="n"/>
+      <c r="F36" s="253" t="n"/>
+      <c r="G36" s="253" t="n"/>
+      <c r="H36" s="253" t="n"/>
+      <c r="I36" s="253" t="n"/>
+      <c r="J36" s="253" t="n"/>
+      <c r="K36" s="253" t="n"/>
+      <c r="L36" s="253" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="70">
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="H26:L26"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="E24:F24"/>
+  <mergeCells count="54">
+    <mergeCell ref="G15:L20"/>
+    <mergeCell ref="A19:F20"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="K2:L3"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="C29:L30"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A17:B18"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="A15:F16"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="G10:H10"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="A29:B30"/>
+    <mergeCell ref="C25:L26"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C6:L6"/>
+    <mergeCell ref="A27:B28"/>
+    <mergeCell ref="C31:L32"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A28:B29"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A24:B27"/>
-    <mergeCell ref="G2:H3"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A34:B35"/>
+    <mergeCell ref="C17:F18"/>
+    <mergeCell ref="C23:L24"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="A31:B32"/>
     <mergeCell ref="I2:J3"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="C20:L20"/>
-    <mergeCell ref="H28:L28"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="C27:L28"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A22:B22"/>
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="A1:F3"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="C34:L35"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="C11:L11"/>
   </mergeCells>
-  <conditionalFormatting sqref="K25:L25">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
-      <formula>"EFFECTIVE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
-      <formula>"INEFFECTIVE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="5">
-      <formula>"PENDING"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="19">
-    <dataValidation sqref="J6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK" promptTitle="불량 유형" prompt="참고 시트 2개은 유형과 무관하게 항상 첨부한다.&#10;어느 자료가 이번 건에 쓸모 있는지는 담당자가 판단한다." type="list">
-      <formula1>"MISSING,POSITION_ERROR,ORIENTATION_ERROR,CRACK"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 협조가 필요한 조치" prompt="담당자 혼자 결정할 수 없는 항목이다. 해당하는 것의 □ 를 ■ 로 바꾸고,&#10;아래 칸에 누구에게 언제 요청했는지 적는다.&#10;&#10;생산 중단 → 생산팀장 · 출하 보류 → 영업/물류 · 재고 선별 → 인력 투입 승인&#10;고객 통보 → 품질보증 책임자 · 설비 정지 → 설비팀&#10;"/>
-    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="① 초동 조치 — 오늘 안에" prompt="격리·선별·출하보류 범위와 완료 시각을 적는다.&#10;영향 받는 job_id / unit_id 범위를 함께 적는다.&#10;&#10;원인이 안 나와도 오늘 회신한다. 여기는 '막았는지'만 쓰는 칸이다.&#10;원인을 없애는 것은 ④ 이고, 이 칸은 확산을 멈추는 칸이다.&#10;"/>
-    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 한 줄 요약 (40자)" prompt="본문을 한 줄로 줄인 것. 예: '배치 하강속도 상향 + 지지 핀 최원거리 슬롯'&#10;본문은 길어서 이 칸에 들어가지 않으므로 핵심 원인만 적는다."/>
-    <dataValidation sqref="C21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="② 발생 원인 — 왜 만들어졌는가" prompt="「불량 근거」의 발생 기록과 검사 이미지를 확인한다.&#10;재현 또는 실물 확인으로 검증한 근거를 적는다.&#10;가설이면 '가설'이라고 표시한다.&#10;"/>
-    <dataValidation sqref="C22" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="③ 유출 원인 — 왜 검사에서 걸리지 않았는가" prompt="「부품 검토자료」의 데이터시트 검사 항목과 대조해 판정 기준의 한계를 적는다.&#10;검사를 안 한 것인지, 했는데 못 걸른 것인지 구분한다.&#10;"/>
-    <dataValidation sqref="C23" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="④ 재발방지 대책 — 원인을 제거하는 영구대책" prompt="레시피·공정조건을 바꾸면 변경 후 recipe_version을 적는다.&#10;부품을 바꾸면 「부품 검토자료」의 대체품 영역의 대체코드를 적는다.&#10;동일 부품을 쓰는 다른 슬롯으로의 수평전개 여부를 포함한다.&#10;&#10;레시피 변경은 변경관리 승인이, 부품 교체는 고객 승인이 필요할 수 있다.&#10;승인 절차가 걸리면 그 일정도 함께 적는다.&#10;"/>
-    <dataValidation sqref="C25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 기간" prompt="대책을 적용하고 다시 집계한 구간. [시작, 끝) 으로 적는다.&#10;"/>
-    <dataValidation sqref="E25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 적용 레시피" prompt="대책을 적용한 뒤 실행한 recipe_version.&#10;이 값이 있어야 적용 전후를 같은 제품 안에서 비교할 수 있다.&#10;"/>
-    <dataValidation sqref="G25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 검사 수량" prompt="부품 기준 검사 건수 (유닛 수 × 해당 부품 슬롯 수).&#10;"/>
-    <dataValidation sqref="G25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation sqref="I25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 검증 불량 수량" prompt=""/>
-    <dataValidation sqref="I25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation sqref="K25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용되지 않는 값" error="다음 중 하나여야 한다: PENDING,EFFECTIVE,INEFFECTIVE" promptTitle="⑤ 판정" prompt="품질 절차에서 정한 판정 기준에 따라 선택한다." type="list">
-      <formula1>"PENDING,EFFECTIVE,INEFFECTIVE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정" prompt="판정 기준과 비교한 결론을 선택한다.&#10;기준은 해당 품질 절차에서 확인한다."/>
-    <dataValidation sqref="C27" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑤ 판정 근거" prompt="재집계 결과를 그렇게 읽은 이유.&#10;"/>
-    <dataValidation sqref="E28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결일" prompt=""/>
-    <dataValidation sqref="C29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="⑥ 종결 의견" prompt="잔여 위험과 종결 승인 의견.&#10;"/>
-    <dataValidation sqref="G25 I25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수량 확인" error="0 이상의 정수를 입력하세요." type="whole" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
+  <dataValidations count="9">
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="납품 추적" prompt="실제 납품업체와 Lot/PO 등 추적정보를 적습니다. 해당 없으면 해당 없음을 기록합니다."/>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="판정 근거" prompt="검사 기준·실제 관찰 결과·근거 기록번호를 적습니다. 원인 미확정 시 추정 원인을 단정하지 않습니다."/>
+    <dataValidation sqref="C23" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="초동조치" prompt="격리·선별·보류 범위, 실제 완료 여부·시각과 담당자를 적습니다. 요청과 완료를 구분합니다."/>
+    <dataValidation sqref="C25" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="발생 원인" prompt="발생 원인과 재현·실물 확인 등 입증 근거를 적습니다. 미확정이면 미확정 및 확인 계획을 적습니다."/>
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="유출 원인" prompt="검출·유출 방지 실패 원인과 확인 근거를 적습니다. 해당 없으면 이유를 적습니다."/>
+    <dataValidation sqref="C29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="재발방지" prompt="원인을 제거하는 조치, 담당자·기한·완료일·적용 범위와 기록번호를 적습니다."/>
+    <dataValidation sqref="C31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="효과 확인" prompt="검증 방법·기간·판정 기준·실제 결과·확인자를 적습니다. 필요한 검사 수량은 본문에 기록합니다. 검증 전에는 종결하지 않습니다."/>
+    <dataValidation sqref="C34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="종결 판정" prompt="효과 확인 후 종결 여부, 승인자·일자, 보류 해제·격리품 처분과 잔여 사항을 적습니다."/>
+    <dataValidation sqref="K5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="문서 상태" error="발행, 진행중, 검증중, 종결 중 선택합니다." type="list">
+      <formula1>"발행,진행중,검증중,종결"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.32" right="0.32" top="0.32" bottom="0.32" header="0.1" footer="0.1"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00233D59"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="186" t="inlineStr">
-        <is>
-          <t>불량 근거 및 납품 추적</t>
-        </is>
-      </c>
-      <c r="B1" s="246" t="n"/>
-      <c r="C1" s="246" t="n"/>
-      <c r="D1" s="246" t="n"/>
-      <c r="E1" s="247" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="187" t="inlineStr">
-        <is>
-          <t>연녹색: 시스템 자동 기입 · 연노랑: 담당자 수동 작성</t>
-        </is>
-      </c>
-      <c r="B2" s="246" t="n"/>
-      <c r="C2" s="246" t="n"/>
-      <c r="D2" s="246" t="n"/>
-      <c r="E2" s="247" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="190" t="inlineStr">
-        <is>
-          <t>01  발행 대상 · 시스템 자동 기입</t>
-        </is>
-      </c>
-      <c r="B3" s="248" t="n"/>
-      <c r="C3" s="248" t="n"/>
-      <c r="D3" s="248" t="n"/>
-      <c r="E3" s="249" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="224" t="inlineStr">
-        <is>
-          <t>문서 {{alert_code}} · 불량 ID {{unit_defect_id}} · Unit {{target_unit_id}}</t>
-        </is>
-      </c>
-      <c r="B4" s="215" t="n"/>
-      <c r="C4" s="215" t="n"/>
-      <c r="D4" s="215" t="n"/>
-      <c r="E4" s="216" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="224" t="inlineStr">
-        <is>
-          <t>슬롯 {{target_slot_code}} · {{defect_type}} · 검사 {{target_inspected_at}}</t>
-        </is>
-      </c>
-      <c r="B5" s="215" t="n"/>
-      <c r="C5" s="215" t="n"/>
-      <c r="D5" s="215" t="n"/>
-      <c r="E5" s="216" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="190" t="inlineStr">
-        <is>
-          <t>02  동일 Job·부품·유형 누적 · 발행 시점 참고</t>
-        </is>
-      </c>
-      <c r="B6" s="248" t="n"/>
-      <c r="C6" s="248" t="n"/>
-      <c r="D6" s="248" t="n"/>
-      <c r="E6" s="249" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="172" t="inlineStr">
-        <is>
-          <t>슬롯</t>
-        </is>
-      </c>
-      <c r="B7" s="172" t="inlineStr">
-        <is>
-          <t>불량 건수</t>
-        </is>
-      </c>
-      <c r="C7" s="172" t="inlineStr">
-        <is>
-          <t>슬롯 불량률</t>
-        </is>
-      </c>
-      <c r="D7" s="172" t="inlineStr">
-        <is>
-          <t>집계 기준</t>
-        </is>
-      </c>
-      <c r="E7" s="172" t="inlineStr">
-        <is>
-          <t>해석</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="214" t="inlineStr">
-        <is>
-          <t>{{slot_code}}</t>
-        </is>
-      </c>
-      <c r="B8" s="214" t="inlineStr">
-        <is>
-          <t>{{count}}</t>
-        </is>
-      </c>
-      <c r="C8" s="214" t="inlineStr">
-        <is>
-          <t>{{slot_rate}}</t>
-        </is>
-      </c>
-      <c r="D8" s="214" t="inlineStr">
-        <is>
-          <t>{{slot_note}}</t>
-        </is>
-      </c>
-      <c r="E8" s="187" t="inlineStr">
-        <is>
-          <t>전체 폐기·공급사 귀책을 뜻하지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="190" t="inlineStr">
-        <is>
-          <t>03  판정·납품 추적 · 당사 담당자 작성</t>
-        </is>
-      </c>
-      <c r="B9" s="248" t="n"/>
-      <c r="C9" s="248" t="n"/>
-      <c r="D9" s="248" t="n"/>
-      <c r="E9" s="249" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="190" t="inlineStr">
-        <is>
-          <t>판정 근거</t>
-        </is>
-      </c>
-      <c r="B10" s="174" t="inlineStr"/>
-      <c r="C10" s="211" t="n"/>
-      <c r="D10" s="211" t="n"/>
-      <c r="E10" s="212" t="n"/>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="190" t="inlineStr">
-        <is>
-          <t>납품 추적</t>
-        </is>
-      </c>
-      <c r="B11" s="174" t="inlineStr"/>
-      <c r="C11" s="211" t="n"/>
-      <c r="D11" s="211" t="n"/>
-      <c r="E11" s="212" t="n"/>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="190" t="inlineStr">
-        <is>
-          <t>영향·격리</t>
-        </is>
-      </c>
-      <c r="B12" s="174" t="inlineStr"/>
-      <c r="C12" s="211" t="n"/>
-      <c r="D12" s="211" t="n"/>
-      <c r="E12" s="212" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="190" t="inlineStr">
-        <is>
-          <t>기능·처분</t>
-        </is>
-      </c>
-      <c r="B13" s="174" t="inlineStr"/>
-      <c r="C13" s="211" t="n"/>
-      <c r="D13" s="211" t="n"/>
-      <c r="E13" s="212" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="190" t="inlineStr">
-        <is>
-          <t>접수·회신</t>
-        </is>
-      </c>
-      <c r="B14" s="174" t="inlineStr"/>
-      <c r="C14" s="211" t="n"/>
-      <c r="D14" s="211" t="n"/>
-      <c r="E14" s="212" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="190" t="inlineStr">
-        <is>
-          <t>정지·손실</t>
-        </is>
-      </c>
-      <c r="B15" s="174" t="inlineStr"/>
-      <c r="C15" s="211" t="n"/>
-      <c r="D15" s="211" t="n"/>
-      <c r="E15" s="212" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="190" t="inlineStr">
-        <is>
-          <t>04  검사 이미지 · 시스템 첨부</t>
-        </is>
-      </c>
-      <c r="B16" s="248" t="n"/>
-      <c r="C16" s="248" t="n"/>
-      <c r="D16" s="248" t="n"/>
-      <c r="E16" s="249" t="n"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="225" t="inlineStr">
-        <is>
-          <t>{{inspection_image_status}} · {{inspection_image_path}}
-SHA-256 {{inspection_image_sha256}}</t>
-        </is>
-      </c>
-      <c r="B17" s="215" t="n"/>
-      <c r="C17" s="215" t="n"/>
-      <c r="D17" s="215" t="n"/>
-      <c r="E17" s="216" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="224" t="inlineStr"/>
-      <c r="B18" s="226" t="n"/>
-      <c r="C18" s="226" t="n"/>
-      <c r="D18" s="226" t="n"/>
-      <c r="E18" s="227" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="228" t="n"/>
-      <c r="B19" s="229" t="n"/>
-      <c r="C19" s="229" t="n"/>
-      <c r="D19" s="229" t="n"/>
-      <c r="E19" s="230" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="228" t="n"/>
-      <c r="B20" s="229" t="n"/>
-      <c r="C20" s="229" t="n"/>
-      <c r="D20" s="229" t="n"/>
-      <c r="E20" s="230" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="228" t="n"/>
-      <c r="B21" s="229" t="n"/>
-      <c r="C21" s="229" t="n"/>
-      <c r="D21" s="229" t="n"/>
-      <c r="E21" s="230" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="228" t="n"/>
-      <c r="B22" s="229" t="n"/>
-      <c r="C22" s="229" t="n"/>
-      <c r="D22" s="229" t="n"/>
-      <c r="E22" s="230" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="231" t="n"/>
-      <c r="B23" s="232" t="n"/>
-      <c r="C23" s="232" t="n"/>
-      <c r="D23" s="232" t="n"/>
-      <c r="E23" s="233" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="32">
-    <mergeCell ref="A8"/>
-    <mergeCell ref="C8"/>
-    <mergeCell ref="C7"/>
-    <mergeCell ref="D8"/>
-    <mergeCell ref="E7"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A13"/>
-    <mergeCell ref="A18:E23"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A15"/>
-    <mergeCell ref="B7"/>
-    <mergeCell ref="A11"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="E8"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B8"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="D7"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="A14"/>
-    <mergeCell ref="A9:E9"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.32" right="0.32" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
+  <pageMargins left="0.32" right="0.32" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 불량 근거&amp;C&amp;8 연녹색: 자동 | 연노랑: 수동&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="008797A7"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="192" t="inlineStr">
-        <is>
-          <t>부품 검토자료 · 내부 참고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="234" t="inlineStr">
-        <is>
-          <t>부품 범주 {{category_label}} · 데이터시트 대조 {{datasheet_match}} · 기준일 {{source_dated_on}} · 조회 {{queried_at}}</t>
-        </is>
-      </c>
-      <c r="B2" s="229" t="n"/>
-      <c r="C2" s="229" t="n"/>
-      <c r="D2" s="229" t="n"/>
-      <c r="E2" s="229" t="n"/>
-      <c r="F2" s="229" t="n"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="250" t="inlineStr">
-        <is>
-          <t>현재 부품  |  데이터시트 대조</t>
-        </is>
-      </c>
-      <c r="B3" s="251" t="n"/>
-      <c r="C3" s="251" t="n"/>
-      <c r="D3" s="251" t="n"/>
-      <c r="E3" s="251" t="n"/>
-      <c r="F3" s="251" t="n"/>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="235" t="inlineStr">
-        <is>
-          <t>현재 MPN</t>
-        </is>
-      </c>
-      <c r="B4" s="235" t="inlineStr">
-        <is>
-          <t>핵심 정격</t>
-        </is>
-      </c>
-      <c r="C4" s="235" t="inlineStr">
-        <is>
-          <t>자료상 공급사</t>
-        </is>
-      </c>
-      <c r="D4" s="236" t="inlineStr">
-        <is>
-          <t>단가(USD)</t>
-        </is>
-      </c>
-      <c r="E4" s="235" t="inlineStr">
-        <is>
-          <t>가격 기준 수량</t>
-        </is>
-      </c>
-      <c r="F4" s="235" t="inlineStr">
-        <is>
-          <t>가격 확인일</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="237" t="inlineStr">
-        <is>
-          <t>{{selected_mpn}}</t>
-        </is>
-      </c>
-      <c r="B5" s="237" t="inlineStr">
-        <is>
-          <t>{{selected_spec}}</t>
-        </is>
-      </c>
-      <c r="C5" s="237" t="inlineStr">
-        <is>
-          <t>{{selected_supplier}}</t>
-        </is>
-      </c>
-      <c r="D5" s="238" t="inlineStr">
-        <is>
-          <t>{{selected_unit_price}}</t>
-        </is>
-      </c>
-      <c r="E5" s="239" t="inlineStr">
-        <is>
-          <t>{{selected_price_basis}}</t>
-        </is>
-      </c>
-      <c r="F5" s="239" t="inlineStr">
-        <is>
-          <t>{{selected_price_checked_at}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1">
-      <c r="A6" s="52" t="n"/>
-      <c r="B6" s="52" t="n"/>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="52" t="n"/>
-      <c r="E6" s="52" t="n"/>
-      <c r="F6" s="52" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="250" t="inlineStr">
-        <is>
-          <t>품질 체크리스트  |  공통 기준 + 부품별 기준</t>
-        </is>
-      </c>
-      <c r="B7" s="251" t="n"/>
-      <c r="C7" s="251" t="n"/>
-      <c r="D7" s="251" t="n"/>
-      <c r="E7" s="251" t="n"/>
-      <c r="F7" s="251" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="235" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B8" s="235" t="inlineStr">
-        <is>
-          <t>확인 항목</t>
-        </is>
-      </c>
-      <c r="C8" s="251" t="n"/>
-      <c r="D8" s="251" t="n"/>
-      <c r="E8" s="235" t="inlineStr">
-        <is>
-          <t>이상 시 조치</t>
-        </is>
-      </c>
-      <c r="F8" s="251" t="n"/>
-    </row>
-    <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="235" t="inlineStr">
-        <is>
-          <t>입고 검사</t>
-        </is>
-      </c>
-      <c r="B9" s="240" t="inlineStr">
-        <is>
-          <t>{{incoming_inspection}}</t>
-        </is>
-      </c>
-      <c r="C9" s="229" t="n"/>
-      <c r="D9" s="229" t="n"/>
-      <c r="E9" s="240" t="inlineStr">
-        <is>
-          <t>{{action_on_anomaly}}</t>
-        </is>
-      </c>
-      <c r="F9" s="229" t="n"/>
-    </row>
-    <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="235" t="inlineStr">
-        <is>
-          <t>조립·보관</t>
-        </is>
-      </c>
-      <c r="B10" s="240" t="inlineStr">
-        <is>
-          <t>{{assembly_control}}</t>
-        </is>
-      </c>
-      <c r="C10" s="229" t="n"/>
-      <c r="D10" s="229" t="n"/>
-      <c r="E10" s="229" t="n"/>
-      <c r="F10" s="229" t="n"/>
-    </row>
-    <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="235" t="inlineStr">
-        <is>
-          <t>기능·신뢰성</t>
-        </is>
-      </c>
-      <c r="B11" s="240" t="inlineStr">
-        <is>
-          <t>{{reliability_test}}</t>
-        </is>
-      </c>
-      <c r="C11" s="229" t="n"/>
-      <c r="D11" s="229" t="n"/>
-      <c r="E11" s="229" t="n"/>
-      <c r="F11" s="229" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="193" t="inlineStr">
-        <is>
-          <t>연녹색: 데이터시트 자동 조회 · 수동 입력란 없음 · 실제 조치 결과는 담당자 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="8" customHeight="1">
-      <c r="A13" s="52" t="n"/>
-      <c r="B13" s="52" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="250" t="inlineStr">
-        <is>
-          <t>대체품 후보  |  적합성 검증·변경 승인 후 적용</t>
-        </is>
-      </c>
-      <c r="B14" s="251" t="n"/>
-      <c r="C14" s="251" t="n"/>
-      <c r="D14" s="251" t="n"/>
-      <c r="E14" s="251" t="n"/>
-      <c r="F14" s="251" t="n"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="241" t="inlineStr">
-        <is>
-          <t>같은 부품 타입이라는 것 외에 검증된 것은 없다 · 동일 정격만으로 drop-in 판단 금지 · 핀/패키지/정격/열/수명 재검증과 변경 승인을 거친 뒤에만 적용한다.</t>
-        </is>
-      </c>
-      <c r="B15" s="251" t="n"/>
-      <c r="C15" s="251" t="n"/>
-      <c r="D15" s="251" t="n"/>
-      <c r="E15" s="251" t="n"/>
-      <c r="F15" s="251" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="234" t="inlineStr">
-        <is>
-          <t>같은 타입 후보 {{candidate_count}}종 · 단가 {{price_range}} · 현재 선정 {{price_selected}} · 호환성 미승인</t>
-        </is>
-      </c>
-      <c r="B16" s="229" t="n"/>
-      <c r="C16" s="229" t="n"/>
-      <c r="D16" s="229" t="n"/>
-      <c r="E16" s="229" t="n"/>
-      <c r="F16" s="229" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="190" t="inlineStr">
-        <is>
-          <t>검토 후보 MPN · 상세 정격·가격은 원본 Components에서 MPN으로 확인</t>
-        </is>
-      </c>
-      <c r="B17" s="248" t="n"/>
-      <c r="C17" s="248" t="n"/>
-      <c r="D17" s="248" t="n"/>
-      <c r="E17" s="248" t="n"/>
-      <c r="F17" s="249" t="n"/>
-    </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="242" t="inlineStr">
-        <is>
-          <t>{{manufacturer_part_number}}</t>
-        </is>
-      </c>
-      <c r="B18" s="226" t="n"/>
-      <c r="C18" s="226" t="n"/>
-      <c r="D18" s="226" t="n"/>
-      <c r="E18" s="226" t="n"/>
-      <c r="F18" s="227" t="n"/>
-    </row>
-    <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="231" t="n"/>
-      <c r="B19" s="232" t="n"/>
-      <c r="C19" s="232" t="n"/>
-      <c r="D19" s="232" t="n"/>
-      <c r="E19" s="232" t="n"/>
-      <c r="F19" s="233" t="n"/>
-    </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="86" t="inlineStr">
-        <is>
-          <t>단가는 데이터시트 기준일의 값이고 발주 근거가 아니다. MOQ·재고·리드타임과 상호호환 판정은 이 문서에 없다 → GET /api/v1/parts/{{part_id}} 또는 구매·품질 담당</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="38" customHeight="1">
-      <c r="A21" s="243" t="inlineStr">
-        <is>
-          <t>원본 {{source_file}}</t>
-        </is>
-      </c>
-      <c r="B21" s="229" t="n"/>
-      <c r="C21" s="229" t="n"/>
-      <c r="D21" s="229" t="n"/>
-      <c r="E21" s="229" t="n"/>
-      <c r="F21" s="229" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="18">
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A18:F19"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F11"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.32" right="0.32" top="0.35" bottom="0.38" header="0.15" footer="0.17"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;L&amp;8 &amp;K627083v2 · 검토용&amp;C&amp;8 연녹색: 자동 | 연노랑: 수동&amp;R&amp;8 &amp;K627083&amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
+++ b/MAIN_SERVER/templates/불량대책서_표준양식_v2.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대책서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="대체품" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="reply_containment">'대책서'!$C$23</definedName>
@@ -18,6 +19,7 @@
     <definedName name="reply_closed_at">'대책서'!$I$33</definedName>
     <definedName name="reply_closure_note">'대책서'!$C$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'대책서'!$A$1:$L$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'대체품'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -544,7 +546,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -993,11 +995,108 @@
         <color rgb="00A6ADB7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6ADB7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6ADB7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6ADB7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6ADB7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6ADB7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6ADB7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6ADB7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6ADB7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6ADB7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A6ADB7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6ADB7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6ADB7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6ADB7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6ADB7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6ADB7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="278">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1743,6 +1842,54 @@
     </xf>
     <xf numFmtId="0" fontId="73" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2993,4 +3140,221 @@
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>현재 부품과 대체품 후보 · 내부 검토용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="294" t="inlineStr">
+        <is>
+          <t>현재 부품: {{part_id}} / {{part_name}} / {{category_label}} · 데이터시트 대조: {{datasheet_match}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>현재 MPN</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>핵심 정격</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>공급사</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>단가 (USD)</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>가격 기준 수량</t>
+        </is>
+      </c>
+      <c r="F3" s="29" t="inlineStr">
+        <is>
+          <t>가격 확인일</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_mpn}}</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_spec}}</t>
+        </is>
+      </c>
+      <c r="C4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_supplier}}</t>
+        </is>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>{{selected_unit_price}}</t>
+        </is>
+      </c>
+      <c r="E4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_price_basis}}</t>
+        </is>
+      </c>
+      <c r="F4" s="39" t="inlineStr">
+        <is>
+          <t>{{selected_price_checked_at}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="295" t="inlineStr">
+        <is>
+          <t>같은 부품 타입이라는 것 외에 검증된 것은 없다 · 동일 정격만으로 drop-in 판단 금지 · 핀/패키지/정격/열/수명 재검증과 변경 승인을 거친 뒤에만 적용한다.</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="296" t="inlineStr">
+        <is>
+          <t>후보 {{candidate_count}}종 · 조회 {{queried_at}} · 데이터시트 기준일 {{source_dated_on}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="297" t="inlineStr">
+        <is>
+          <t>대체품 후보 목록 · 호환성 검증 및 변경 승인 후 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>제조사 / P/N</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>핵심 정격</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>공급사</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>단가 (USD)</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>가격 기준 수량</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>가격 확인일</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>{{manufacturer_part_number}}</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>{{key_spec}}</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>{{supplier}}</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>{{unit_price}}</t>
+        </is>
+      </c>
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>{{price_basis}}</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="inlineStr">
+        <is>
+          <t>{{price_checked_at}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="298" t="inlineStr">
+        <is>
+          <t>단가는 데이터시트 기준일의 참고값입니다. 발주 전 구매·품질 담당자가 최신 가격·재고·납기와 적합성을 확인합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="299" t="inlineStr">
+        <is>
+          <t>원본: {{source_file}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="0"/>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>